--- a/source_data/SourceData_Fig3.xlsx
+++ b/source_data/SourceData_Fig3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -634,30 +634,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fe optimum</t>
+          <t>Ru/C catalyst's own bed (squares and bars; 3.2 wt% Ru, 1,000 and 500 kg m-3)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>figures/composite/fig2/fig2_pressure_envelopes.csv</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>figures/composite/fig2/fig2_ru_bed_sensitivity.csv</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>lower panel: alpha_star_supported_bed</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>waterfall Fe -&gt; Ru</t>
+          <t>Fe optimum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>analysis/supervisor_2026_09_20/nh3_cost_decomposition.csv</t>
+          <t>figures/composite/fig2/fig2_pressure_envelopes.csv</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -670,7 +674,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>totals</t>
+          <t>waterfall Fe -&gt; Ru</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -683,17 +687,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1,000 descriptor draws</t>
+          <t>totals</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/closure/mc_draws.csv</t>
+          <t>analysis/supervisor_2026_09_20/nh3_cost_decomposition.csv</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -706,12 +710,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fe bed-feasibility interval and canonical point</t>
+          <t>1,000 descriptor draws</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/closure/mc_draws.csv + figures/composite/fig1/fig1_metals.csv</t>
+          <t>provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/closure/mc_draws.csv</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -719,17 +723,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>decision endpoints (% of 1,000 draws)</t>
+          <t>Fe bed-feasibility interval and canonical point</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>analysis/supervisor_2026_09_20/f3_panel_summary.csv</t>
+          <t>provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/closure/mc_draws.csv + figures/composite/fig1/fig1_metals.csv</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -737,17 +741,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>g</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ru - Fe cost gap, 5,000 joint cost draws</t>
+          <t>decision endpoints (% of 1,000 draws)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>analysis/supervisor_2026_09_20/nh3_cost_mc_histogram.csv</t>
+          <t>analysis/supervisor_2026_09_20/f3_panel_summary.csv</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -760,15 +764,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Ru - Fe cost gap, 5,000 joint cost draws</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>analysis/supervisor_2026_09_20/nh3_cost_mc_histogram.csv</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>lines</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>analysis/supervisor_2026_09_20/f3_panel_summary.csv</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18403,7 +18425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M272"/>
+  <dimension ref="A1:M288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22353,36 +22375,574 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>Fe optimum</t>
+          <t>Ru/C catalyst's own bed (squares and bars; 3.2 wt% Ru, 1,000 and 500 kg m-3)</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
+          <t>source: figures/composite/fig2/fig2_ru_bed_sensitivity.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>lower panel: alpha_star_supported_bed</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B272" s="1" t="inlineStr">
+        <is>
+          <t>rho_bed_kg_m3</t>
+        </is>
+      </c>
+      <c r="C272" s="1" t="inlineStr">
+        <is>
+          <t>bed_factor</t>
+        </is>
+      </c>
+      <c r="D272" s="1" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="E272" s="1" t="inlineStr">
+        <is>
+          <t>delta_vs_benchmark_bed</t>
+        </is>
+      </c>
+      <c r="F272" s="1" t="inlineStr">
+        <is>
+          <t>T_C</t>
+        </is>
+      </c>
+      <c r="G272" s="1" t="inlineStr">
+        <is>
+          <t>P_bar</t>
+        </is>
+      </c>
+      <c r="H272" s="1" t="inlineStr">
+        <is>
+          <t>Tsep_C</t>
+        </is>
+      </c>
+      <c r="I272" s="1" t="inlineStr">
+        <is>
+          <t>V_m3</t>
+        </is>
+      </c>
+      <c r="J272" s="1" t="inlineStr">
+        <is>
+          <t>Fe_reference</t>
+        </is>
+      </c>
+      <c r="K272" s="1" t="inlineStr">
+        <is>
+          <t>Fe_reference_cost</t>
+        </is>
+      </c>
+      <c r="L272" s="1" t="inlineStr">
+        <is>
+          <t>gap_to_Fe_reference</t>
+        </is>
+      </c>
+      <c r="M272" s="1" t="inlineStr">
+        <is>
+          <t>alpha_star_supported_bed</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>500</v>
+      </c>
+      <c r="C273" t="n">
+        <v>10.15767045454546</v>
+      </c>
+      <c r="D273" t="n">
+        <v>18.26330851308655</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0.3133392570384679</v>
+      </c>
+      <c r="F273" t="n">
+        <v>450</v>
+      </c>
+      <c r="G273" t="n">
+        <v>220</v>
+      </c>
+      <c r="H273" t="n">
+        <v>20</v>
+      </c>
+      <c r="I273" t="n">
+        <v>5.403550401038705</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="K273" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="L273" t="n">
+        <v>2.971603836465405</v>
+      </c>
+      <c r="M273" t="n">
+        <v>22.40458888846904</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C274" t="n">
+        <v>5.078835227272728</v>
+      </c>
+      <c r="D274" t="n">
+        <v>18.09591294859322</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.1459436925451349</v>
+      </c>
+      <c r="F274" t="n">
+        <v>450</v>
+      </c>
+      <c r="G274" t="n">
+        <v>220</v>
+      </c>
+      <c r="H274" t="n">
+        <v>20</v>
+      </c>
+      <c r="I274" t="n">
+        <v>2.701775200519353</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="K274" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="L274" t="n">
+        <v>2.804208271972072</v>
+      </c>
+      <c r="M274" t="n">
+        <v>20.35135231032596</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>supp_rec90</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>500</v>
+      </c>
+      <c r="C275" t="n">
+        <v>10.15767045454546</v>
+      </c>
+      <c r="D275" t="n">
+        <v>16.43801872529701</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.7671643557893137</v>
+      </c>
+      <c r="F275" t="n">
+        <v>450</v>
+      </c>
+      <c r="G275" t="n">
+        <v>220</v>
+      </c>
+      <c r="H275" t="n">
+        <v>30</v>
+      </c>
+      <c r="I275" t="n">
+        <v>11.44278085370695</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="K275" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="L275" t="n">
+        <v>1.146314048675869</v>
+      </c>
+      <c r="M275" t="n">
+        <v>5.705909208804983</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>supp_rec90</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C276" t="n">
+        <v>5.078835227272728</v>
+      </c>
+      <c r="D276" t="n">
+        <v>16.04089196424533</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.3700375947376297</v>
+      </c>
+      <c r="F276" t="n">
+        <v>450</v>
+      </c>
+      <c r="G276" t="n">
+        <v>210</v>
+      </c>
+      <c r="H276" t="n">
+        <v>30</v>
+      </c>
+      <c r="I276" t="n">
+        <v>7.070246160595759</v>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="K276" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="L276" t="n">
+        <v>0.749187287624185</v>
+      </c>
+      <c r="M276" t="n">
+        <v>3.778368991540755</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>supp_rec94</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>500</v>
+      </c>
+      <c r="C277" t="n">
+        <v>10.15767045454546</v>
+      </c>
+      <c r="D277" t="n">
+        <v>16.31527630392829</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.8302253475652712</v>
+      </c>
+      <c r="F277" t="n">
+        <v>450</v>
+      </c>
+      <c r="G277" t="n">
+        <v>215</v>
+      </c>
+      <c r="H277" t="n">
+        <v>30</v>
+      </c>
+      <c r="I277" t="n">
+        <v>12.69088984299629</v>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="K277" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="L277" t="n">
+        <v>1.023571627307145</v>
+      </c>
+      <c r="M277" t="n">
+        <v>4.971667553199788</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>supp_rec94</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C278" t="n">
+        <v>5.078835227272728</v>
+      </c>
+      <c r="D278" t="n">
+        <v>15.88797774037817</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.4029267840151522</v>
+      </c>
+      <c r="F278" t="n">
+        <v>450</v>
+      </c>
+      <c r="G278" t="n">
+        <v>205</v>
+      </c>
+      <c r="H278" t="n">
+        <v>30</v>
+      </c>
+      <c r="I278" t="n">
+        <v>7.918918441303689</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="K278" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="L278" t="n">
+        <v>0.5962730637570264</v>
+      </c>
+      <c r="M278" t="n">
+        <v>3.037358223345998</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>kaap90</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>500</v>
+      </c>
+      <c r="C279" t="n">
+        <v>10.15767045454546</v>
+      </c>
+      <c r="D279" t="n">
+        <v>19.31962114915337</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0.4092221174208603</v>
+      </c>
+      <c r="F279" t="n">
+        <v>425</v>
+      </c>
+      <c r="G279" t="n">
+        <v>90</v>
+      </c>
+      <c r="H279" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I279" t="n">
+        <v>17.75895975672051</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="K279" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="L279" t="n">
+        <v>0.2509325372600521</v>
+      </c>
+      <c r="M279" t="n">
+        <v>1.390070480229767</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>kaap90</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C280" t="n">
+        <v>5.078835227272728</v>
+      </c>
+      <c r="D280" t="n">
+        <v>19.09458074345399</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.1841817117214788</v>
+      </c>
+      <c r="F280" t="n">
+        <v>425</v>
+      </c>
+      <c r="G280" t="n">
+        <v>90</v>
+      </c>
+      <c r="H280" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I280" t="n">
+        <v>8.879479878360257</v>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="K280" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="L280" t="n">
+        <v>0.0258921315606706</v>
+      </c>
+      <c r="M280" t="n">
+        <v>1.040586605201643</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>kaap94</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>500</v>
+      </c>
+      <c r="C281" t="n">
+        <v>10.15767045454546</v>
+      </c>
+      <c r="D281" t="n">
+        <v>19.14310400325828</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.6145217380211001</v>
+      </c>
+      <c r="F281" t="n">
+        <v>425</v>
+      </c>
+      <c r="G281" t="n">
+        <v>90</v>
+      </c>
+      <c r="H281" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I281" t="n">
+        <v>17.75895975672051</v>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="K281" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="L281" t="n">
+        <v>0.07441539136496179</v>
+      </c>
+      <c r="M281" t="n">
+        <v>1.115155511981518</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>kaap94</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C282" t="n">
+        <v>5.078835227272728</v>
+      </c>
+      <c r="D282" t="n">
+        <v>18.91806359755891</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0.3894813323217185</v>
+      </c>
+      <c r="F282" t="n">
+        <v>425</v>
+      </c>
+      <c r="G282" t="n">
+        <v>90</v>
+      </c>
+      <c r="H282" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I282" t="n">
+        <v>8.879479878360257</v>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="K282" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="L282" t="n">
+        <v>-0.1506250143344196</v>
+      </c>
+      <c r="M282" t="n">
+        <v>0.7640273926323318</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
           <t>source: figures/composite/fig2/fig2_pressure_envelopes.csv</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="1" t="inlineStr">
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="B271" s="1" t="inlineStr">
+      <c r="B287" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
+    <row r="288">
+      <c r="A288" t="inlineStr">
         <is>
           <t>Fe cost USD/t</t>
         </is>
       </c>
-      <c r="B272" t="n">
+      <c r="B288" t="n">
         <v>15.29170467662114</v>
       </c>
     </row>

--- a/source_data/SourceData_Fig3.xlsx
+++ b/source_data/SourceData_Fig3.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ru/C catalyst's own bed (squares and bars; 3.2 wt% Ru, 1,000 and 500 kg m-3)</t>
+          <t>Ru/C catalyst's own bed (squares: 8 wt% Ru, 490 kg m-3; bars: 5-10 wt% Ru, 430-550 kg m-3)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -18425,7 +18425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M288"/>
+  <dimension ref="A1:N323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22048,13 +22048,13 @@
         <v>53852.5</v>
       </c>
       <c r="F259" t="n">
-        <v>22.03059478781101</v>
+        <v>22.03059478781103</v>
       </c>
       <c r="G259" t="n">
-        <v>6.738890111189868</v>
+        <v>6.738890111189885</v>
       </c>
       <c r="H259" t="n">
-        <v>201.2234429878986</v>
+        <v>201.2234429879013</v>
       </c>
       <c r="I259" t="n">
         <v>450</v>
@@ -22066,10 +22066,10 @@
         <v>25</v>
       </c>
       <c r="L259" t="n">
-        <v>0.0660321094260842</v>
+        <v>0.0660321094260847</v>
       </c>
       <c r="M259" t="n">
-        <v>1.833375222075018</v>
+        <v>1.833375222075033</v>
       </c>
     </row>
     <row r="260">
@@ -22093,13 +22093,13 @@
         <v>4895.681818181818</v>
       </c>
       <c r="F260" t="n">
-        <v>17.94996925604808</v>
+        <v>17.9499692560481</v>
       </c>
       <c r="G260" t="n">
-        <v>2.658264579426937</v>
+        <v>2.658264579426952</v>
       </c>
       <c r="H260" t="n">
-        <v>18.48410396774684</v>
+        <v>18.48410396774704</v>
       </c>
       <c r="I260" t="n">
         <v>450</v>
@@ -22111,10 +22111,10 @@
         <v>20</v>
       </c>
       <c r="L260" t="n">
-        <v>0.5319674845939377</v>
+        <v>0.5319674845939432</v>
       </c>
       <c r="M260" t="n">
-        <v>1.342729680620329</v>
+        <v>1.342729680620343</v>
       </c>
     </row>
     <row r="261">
@@ -22138,13 +22138,13 @@
         <v>489.5681818181818</v>
       </c>
       <c r="F261" t="n">
-        <v>15.6708543695077</v>
+        <v>15.67085436950771</v>
       </c>
       <c r="G261" t="n">
-        <v>0.3791496928865552</v>
+        <v>0.3791496928865676</v>
       </c>
       <c r="H261" t="n">
-        <v>2.234218129677315</v>
+        <v>2.234218129677338</v>
       </c>
       <c r="I261" t="n">
         <v>450</v>
@@ -22156,55 +22156,55 @@
         <v>30</v>
       </c>
       <c r="L261" t="n">
-        <v>1.756687007548483</v>
+        <v>1.756687007548503</v>
       </c>
       <c r="M261" t="n">
-        <v>0.4434022478640671</v>
+        <v>0.443402247864072</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>supp_rec94</t>
+          <t>supp_rec97</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Supported Ru/C, 94% recovery</t>
+          <t>Supported Ru/C, 97% recovery</t>
         </is>
       </c>
       <c r="C262" t="n">
         <v>11</v>
       </c>
       <c r="D262" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="E262" t="n">
-        <v>293.7409090909093</v>
+        <v>146.8704545454547</v>
       </c>
       <c r="F262" t="n">
-        <v>15.48505095636302</v>
+        <v>15.23737873226116</v>
       </c>
       <c r="G262" t="n">
-        <v>0.1933462797418741</v>
+        <v>-0.0543259443599861</v>
       </c>
       <c r="H262" t="n">
-        <v>1.494309561728353</v>
+        <v>0.9357377150328882</v>
       </c>
       <c r="I262" t="n">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="J262" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="K262" t="n">
         <v>30</v>
       </c>
       <c r="L262" t="n">
-        <v>1.992620830122429</v>
+        <v>6.237550738484852</v>
       </c>
       <c r="M262" t="n">
-        <v>0.3017723310141798</v>
+        <v>0.4723227313788896</v>
       </c>
     </row>
     <row r="263">
@@ -22231,7 +22231,7 @@
         <v>18.91039903173252</v>
       </c>
       <c r="G263" t="n">
-        <v>3.618694355111369</v>
+        <v>3.618694355111376</v>
       </c>
       <c r="H263" t="n">
         <v/>
@@ -22246,37 +22246,37 @@
         <v>-20</v>
       </c>
       <c r="L263" t="n">
-        <v>1.748329977448083</v>
+        <v>1.748329977448104</v>
       </c>
       <c r="M263" t="n">
-        <v>0.4412928647377263</v>
+        <v>0.4412928647377318</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>kaap94</t>
+          <t>kaap97</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Supported Ru/C, 94% recovery, KAAP loop (90 bar, Tsep -20 C)</t>
+          <t>Supported Ru/C, 97% recovery, KAAP loop (90 bar, Tsep -20 C)</t>
         </is>
       </c>
       <c r="C264" t="n">
         <v>11</v>
       </c>
       <c r="D264" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="E264" t="n">
-        <v>293.7409090909093</v>
+        <v>146.8704545454547</v>
       </c>
       <c r="F264" t="n">
-        <v>18.52858226523718</v>
+        <v>18.15699154755242</v>
       </c>
       <c r="G264" t="n">
-        <v>3.236877588616039</v>
+        <v>2.865286870931272</v>
       </c>
       <c r="H264" t="n">
         <v/>
@@ -22291,10 +22291,10 @@
         <v>-20</v>
       </c>
       <c r="L264" t="n">
-        <v>4.907271663047357</v>
+        <v>4.907271663047397</v>
       </c>
       <c r="M264" t="n">
-        <v>0.7431814353695402</v>
+        <v>0.3715907176847731</v>
       </c>
     </row>
     <row r="265">
@@ -22333,10 +22333,10 @@
         <v>-20</v>
       </c>
       <c r="L265" t="n">
-        <v>21.64633610219303</v>
+        <v>21.64633610219298</v>
       </c>
       <c r="M265" t="n">
-        <v>0.08928216263404889</v>
+        <v>0.0892821626340487</v>
       </c>
     </row>
     <row r="266">
@@ -22375,7 +22375,7 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>Ru/C catalyst's own bed (squares and bars; 3.2 wt% Ru, 1,000 and 500 kg m-3)</t>
+          <t>Ru/C catalyst's own bed (squares: 8 wt% Ru, 490 kg m-3; bars: 5-10 wt% Ru, 430-550 kg m-3)</t>
         </is>
       </c>
     </row>
@@ -22401,60 +22401,65 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
+          <t>w_Ru</t>
+        </is>
+      </c>
+      <c r="C272" s="1" t="inlineStr">
+        <is>
           <t>rho_bed_kg_m3</t>
         </is>
       </c>
-      <c r="C272" s="1" t="inlineStr">
+      <c r="D272" s="1" t="inlineStr">
         <is>
           <t>bed_factor</t>
         </is>
       </c>
-      <c r="D272" s="1" t="inlineStr">
+      <c r="E272" s="1" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
       </c>
-      <c r="E272" s="1" t="inlineStr">
+      <c r="F272" s="1" t="inlineStr">
         <is>
           <t>delta_vs_benchmark_bed</t>
         </is>
       </c>
-      <c r="F272" s="1" t="inlineStr">
+      <c r="G272" s="1" t="inlineStr">
         <is>
           <t>T_C</t>
         </is>
       </c>
-      <c r="G272" s="1" t="inlineStr">
+      <c r="H272" s="1" t="inlineStr">
         <is>
           <t>P_bar</t>
         </is>
       </c>
-      <c r="H272" s="1" t="inlineStr">
+      <c r="I272" s="1" t="inlineStr">
         <is>
           <t>Tsep_C</t>
         </is>
       </c>
-      <c r="I272" s="1" t="inlineStr">
+      <c r="J272" s="1" t="inlineStr">
         <is>
           <t>V_m3</t>
         </is>
       </c>
-      <c r="J272" s="1" t="inlineStr">
+      <c r="K272" s="1" t="inlineStr">
         <is>
           <t>Fe_reference</t>
         </is>
       </c>
-      <c r="K272" s="1" t="inlineStr">
+      <c r="L272" s="1" t="inlineStr">
         <is>
           <t>Fe_reference_cost</t>
         </is>
       </c>
-      <c r="L272" s="1" t="inlineStr">
+      <c r="M272" s="1" t="inlineStr">
         <is>
           <t>gap_to_Fe_reference</t>
         </is>
       </c>
-      <c r="M272" s="1" t="inlineStr">
+      <c r="N272" s="1" t="inlineStr">
         <is>
           <t>alpha_star_supported_bed</t>
         </is>
@@ -22467,42 +22472,45 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>500</v>
+        <v>0.05</v>
       </c>
       <c r="C273" t="n">
-        <v>10.15767045454546</v>
+        <v>430</v>
       </c>
       <c r="D273" t="n">
-        <v>18.26330851308655</v>
+        <v>7.559196617336151</v>
       </c>
       <c r="E273" t="n">
-        <v>0.3133392570384679</v>
+        <v>18.17808825112052</v>
       </c>
       <c r="F273" t="n">
-        <v>450</v>
+        <v>0.2281189950724247</v>
       </c>
       <c r="G273" t="n">
+        <v>450</v>
+      </c>
+      <c r="H273" t="n">
         <v>220</v>
       </c>
-      <c r="H273" t="n">
+      <c r="I273" t="n">
         <v>20</v>
       </c>
-      <c r="I273" t="n">
-        <v>5.403550401038705</v>
-      </c>
-      <c r="J273" t="inlineStr">
+      <c r="J273" t="n">
+        <v>4.021246810075357</v>
+      </c>
+      <c r="K273" t="inlineStr">
         <is>
           <t>Fe optimum</t>
         </is>
       </c>
-      <c r="K273" t="n">
+      <c r="L273" t="n">
         <v>15.29170467662114</v>
       </c>
-      <c r="L273" t="n">
-        <v>2.971603836465405</v>
-      </c>
       <c r="M273" t="n">
-        <v>22.40458888846904</v>
+        <v>2.886383574499376</v>
+      </c>
+      <c r="N273" t="n">
+        <v>21.36770571649332</v>
       </c>
     </row>
     <row r="274">
@@ -22512,437 +22520,2144 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>1000</v>
+        <v>0.05</v>
       </c>
       <c r="C274" t="n">
-        <v>5.078835227272728</v>
+        <v>490</v>
       </c>
       <c r="D274" t="n">
-        <v>18.09591294859322</v>
+        <v>6.633580705009276</v>
       </c>
       <c r="E274" t="n">
-        <v>0.1459436925451349</v>
+        <v>18.1475857989463</v>
       </c>
       <c r="F274" t="n">
-        <v>450</v>
+        <v>0.1976165428982064</v>
       </c>
       <c r="G274" t="n">
+        <v>450</v>
+      </c>
+      <c r="H274" t="n">
         <v>220</v>
       </c>
-      <c r="H274" t="n">
+      <c r="I274" t="n">
         <v>20</v>
       </c>
-      <c r="I274" t="n">
-        <v>2.701775200519353</v>
-      </c>
-      <c r="J274" t="inlineStr">
+      <c r="J274" t="n">
+        <v>3.528849241494701</v>
+      </c>
+      <c r="K274" t="inlineStr">
         <is>
           <t>Fe optimum</t>
         </is>
       </c>
-      <c r="K274" t="n">
+      <c r="L274" t="n">
         <v>15.29170467662114</v>
       </c>
-      <c r="L274" t="n">
-        <v>2.804208271972072</v>
-      </c>
       <c r="M274" t="n">
-        <v>20.35135231032596</v>
+        <v>2.855881122325158</v>
+      </c>
+      <c r="N274" t="n">
+        <v>20.99255384200304</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>supp_rec90</t>
+          <t>supported</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>500</v>
+        <v>0.05</v>
       </c>
       <c r="C275" t="n">
-        <v>10.15767045454546</v>
+        <v>550</v>
       </c>
       <c r="D275" t="n">
-        <v>16.43801872529701</v>
+        <v>5.909917355371901</v>
       </c>
       <c r="E275" t="n">
-        <v>0.7671643557893137</v>
+        <v>18.12362266669823</v>
       </c>
       <c r="F275" t="n">
-        <v>450</v>
+        <v>0.1736534106501324</v>
       </c>
       <c r="G275" t="n">
+        <v>450</v>
+      </c>
+      <c r="H275" t="n">
         <v>220</v>
       </c>
-      <c r="H275" t="n">
-        <v>30</v>
-      </c>
       <c r="I275" t="n">
-        <v>11.44278085370695</v>
-      </c>
-      <c r="J275" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="J275" t="n">
+        <v>3.143883869695279</v>
+      </c>
+      <c r="K275" t="inlineStr">
         <is>
           <t>Fe optimum</t>
         </is>
       </c>
-      <c r="K275" t="n">
+      <c r="L275" t="n">
         <v>15.29170467662114</v>
       </c>
-      <c r="L275" t="n">
-        <v>1.146314048675869</v>
-      </c>
       <c r="M275" t="n">
-        <v>5.705909208804983</v>
+        <v>2.831917990077084</v>
+      </c>
+      <c r="N275" t="n">
+        <v>20.69614240487593</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>supp_rec90</t>
+          <t>supported</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>1000</v>
+        <v>0.08</v>
       </c>
       <c r="C276" t="n">
-        <v>5.078835227272728</v>
+        <v>430</v>
       </c>
       <c r="D276" t="n">
-        <v>16.04089196424533</v>
+        <v>4.724497885835096</v>
       </c>
       <c r="E276" t="n">
-        <v>0.3700375947376297</v>
+        <v>18.08401494971733</v>
       </c>
       <c r="F276" t="n">
-        <v>450</v>
+        <v>0.1340456936692362</v>
       </c>
       <c r="G276" t="n">
-        <v>210</v>
+        <v>450</v>
       </c>
       <c r="H276" t="n">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="I276" t="n">
-        <v>7.070246160595759</v>
-      </c>
-      <c r="J276" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="J276" t="n">
+        <v>2.513279256297098</v>
+      </c>
+      <c r="K276" t="inlineStr">
         <is>
           <t>Fe optimum</t>
         </is>
       </c>
-      <c r="K276" t="n">
+      <c r="L276" t="n">
         <v>15.29170467662114</v>
       </c>
-      <c r="L276" t="n">
-        <v>0.749187287624185</v>
-      </c>
       <c r="M276" t="n">
-        <v>3.778368991540755</v>
+        <v>2.792310273096188</v>
+      </c>
+      <c r="N276" t="n">
+        <v>20.20257682776744</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>supp_rec94</t>
+          <t>supported</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>500</v>
+        <v>0.08</v>
       </c>
       <c r="C277" t="n">
-        <v>10.15767045454546</v>
+        <v>490</v>
       </c>
       <c r="D277" t="n">
-        <v>16.31527630392829</v>
+        <v>4.145987940630798</v>
       </c>
       <c r="E277" t="n">
-        <v>0.8302253475652712</v>
+        <v>18.06444592653087</v>
       </c>
       <c r="F277" t="n">
-        <v>450</v>
+        <v>0.1144766704827731</v>
       </c>
       <c r="G277" t="n">
-        <v>215</v>
+        <v>450</v>
       </c>
       <c r="H277" t="n">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="I277" t="n">
-        <v>12.69088984299629</v>
-      </c>
-      <c r="J277" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="J277" t="n">
+        <v>2.205530775934188</v>
+      </c>
+      <c r="K277" t="inlineStr">
         <is>
           <t>Fe optimum</t>
         </is>
       </c>
-      <c r="K277" t="n">
+      <c r="L277" t="n">
         <v>15.29170467662114</v>
       </c>
-      <c r="L277" t="n">
-        <v>1.023571627307145</v>
-      </c>
       <c r="M277" t="n">
-        <v>4.971667553199788</v>
+        <v>2.772741249909725</v>
+      </c>
+      <c r="N277" t="n">
+        <v>19.95683618142185</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>supp_rec94</t>
+          <t>supported</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>1000</v>
+        <v>0.08</v>
       </c>
       <c r="C278" t="n">
-        <v>5.078835227272728</v>
+        <v>550</v>
       </c>
       <c r="D278" t="n">
-        <v>15.88797774037817</v>
+        <v>3.693698347107438</v>
       </c>
       <c r="E278" t="n">
-        <v>0.4029267840151522</v>
+        <v>18.04898887199468</v>
       </c>
       <c r="F278" t="n">
-        <v>450</v>
+        <v>0.09901961594657741</v>
       </c>
       <c r="G278" t="n">
-        <v>205</v>
+        <v>450</v>
       </c>
       <c r="H278" t="n">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="I278" t="n">
-        <v>7.918918441303689</v>
-      </c>
-      <c r="J278" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="J278" t="n">
+        <v>1.964927418559549</v>
+      </c>
+      <c r="K278" t="inlineStr">
         <is>
           <t>Fe optimum</t>
         </is>
       </c>
-      <c r="K278" t="n">
+      <c r="L278" t="n">
         <v>15.29170467662114</v>
       </c>
-      <c r="L278" t="n">
-        <v>0.5962730637570264</v>
-      </c>
       <c r="M278" t="n">
-        <v>3.037358223345998</v>
+        <v>2.757284195373529</v>
+      </c>
+      <c r="N278" t="n">
+        <v>19.76173333750837</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>kaap90</t>
+          <t>supported</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>500</v>
+        <v>0.1</v>
       </c>
       <c r="C279" t="n">
-        <v>10.15767045454546</v>
+        <v>430</v>
       </c>
       <c r="D279" t="n">
-        <v>19.31962114915337</v>
+        <v>3.779598308668076</v>
       </c>
       <c r="E279" t="n">
-        <v>0.4092221174208603</v>
+        <v>18.05193703319081</v>
       </c>
       <c r="F279" t="n">
-        <v>425</v>
+        <v>0.1019677771427112</v>
       </c>
       <c r="G279" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="H279" t="n">
-        <v>-20</v>
+        <v>220</v>
       </c>
       <c r="I279" t="n">
-        <v>17.75895975672051</v>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="K279" t="n">
-        <v>19.06868861189332</v>
+        <v>20</v>
+      </c>
+      <c r="J279" t="n">
+        <v>2.010623405037678</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
       </c>
       <c r="L279" t="n">
-        <v>0.2509325372600521</v>
+        <v>15.29170467662114</v>
       </c>
       <c r="M279" t="n">
-        <v>1.390070480229767</v>
+        <v>2.760232356569663</v>
+      </c>
+      <c r="N279" t="n">
+        <v>19.79901811274726</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>kaap90</t>
+          <t>supported</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>1000</v>
+        <v>0.1</v>
       </c>
       <c r="C280" t="n">
-        <v>5.078835227272728</v>
+        <v>490</v>
       </c>
       <c r="D280" t="n">
-        <v>19.09458074345399</v>
+        <v>3.316790352504638</v>
       </c>
       <c r="E280" t="n">
-        <v>0.1841817117214788</v>
+        <v>18.03597214409293</v>
       </c>
       <c r="F280" t="n">
-        <v>425</v>
+        <v>0.08600288804483459</v>
       </c>
       <c r="G280" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="H280" t="n">
-        <v>-20</v>
+        <v>220</v>
       </c>
       <c r="I280" t="n">
-        <v>8.879479878360257</v>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="K280" t="n">
-        <v>19.06868861189332</v>
+        <v>20</v>
+      </c>
+      <c r="J280" t="n">
+        <v>1.76442462074735</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
       </c>
       <c r="L280" t="n">
-        <v>0.0258921315606706</v>
+        <v>15.29170467662114</v>
       </c>
       <c r="M280" t="n">
-        <v>1.040586605201643</v>
+        <v>2.744267467471786</v>
+      </c>
+      <c r="N280" t="n">
+        <v>19.59668043639056</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>kaap94</t>
+          <t>supported</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>500</v>
+        <v>0.1</v>
       </c>
       <c r="C281" t="n">
-        <v>10.15767045454546</v>
+        <v>550</v>
       </c>
       <c r="D281" t="n">
-        <v>19.14310400325828</v>
+        <v>2.95495867768595</v>
       </c>
       <c r="E281" t="n">
-        <v>0.6145217380211001</v>
+        <v>18.02333019080553</v>
       </c>
       <c r="F281" t="n">
-        <v>425</v>
+        <v>0.0733609347574315</v>
       </c>
       <c r="G281" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="H281" t="n">
-        <v>-20</v>
+        <v>220</v>
       </c>
       <c r="I281" t="n">
-        <v>17.75895975672051</v>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="K281" t="n">
-        <v>19.06868861189332</v>
+        <v>20</v>
+      </c>
+      <c r="J281" t="n">
+        <v>1.57194193484764</v>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
       </c>
       <c r="L281" t="n">
-        <v>0.07441539136496179</v>
+        <v>15.29170467662114</v>
       </c>
       <c r="M281" t="n">
-        <v>1.115155511981518</v>
+        <v>2.731625514184384</v>
+      </c>
+      <c r="N281" t="n">
+        <v>19.43565716567129</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>kaap94</t>
+          <t>supp_rec90</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>1000</v>
+        <v>0.05</v>
       </c>
       <c r="C282" t="n">
-        <v>5.078835227272728</v>
+        <v>430</v>
       </c>
       <c r="D282" t="n">
-        <v>18.91806359755891</v>
+        <v>7.559196617336151</v>
       </c>
       <c r="E282" t="n">
-        <v>0.3894813323217185</v>
+        <v>16.24160844932956</v>
       </c>
       <c r="F282" t="n">
-        <v>425</v>
+        <v>0.5707540798218496</v>
       </c>
       <c r="G282" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="H282" t="n">
-        <v>-20</v>
+        <v>215</v>
       </c>
       <c r="I282" t="n">
-        <v>8.879479878360257</v>
-      </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="K282" t="n">
-        <v>19.06868861189332</v>
+        <v>30</v>
+      </c>
+      <c r="J282" t="n">
+        <v>9.444383138974077</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
       </c>
       <c r="L282" t="n">
-        <v>-0.1506250143344196</v>
+        <v>15.29170467662114</v>
       </c>
       <c r="M282" t="n">
-        <v>0.7640273926323318</v>
+        <v>0.9499037727084172</v>
+      </c>
+      <c r="N282" t="n">
+        <v>4.718376739031267</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>supp_rec90</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C283" t="n">
+        <v>490</v>
+      </c>
+      <c r="D283" t="n">
+        <v>6.633580705009276</v>
+      </c>
+      <c r="E283" t="n">
+        <v>16.16854033282638</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0.4976859633186699</v>
+      </c>
+      <c r="G283" t="n">
+        <v>450</v>
+      </c>
+      <c r="H283" t="n">
+        <v>210</v>
+      </c>
+      <c r="I283" t="n">
+        <v>30</v>
+      </c>
+      <c r="J283" t="n">
+        <v>9.234607230165985</v>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L283" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M283" t="n">
+        <v>0.8768356562052375</v>
+      </c>
+      <c r="N283" t="n">
+        <v>4.367213315780148</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>supp_rec90</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C284" t="n">
+        <v>550</v>
+      </c>
+      <c r="D284" t="n">
+        <v>5.909917355371901</v>
+      </c>
+      <c r="E284" t="n">
+        <v>16.10896375627107</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0.4381093867633616</v>
+      </c>
+      <c r="G284" t="n">
+        <v>450</v>
+      </c>
+      <c r="H284" t="n">
+        <v>210</v>
+      </c>
+      <c r="I284" t="n">
+        <v>30</v>
+      </c>
+      <c r="J284" t="n">
+        <v>8.227195532329695</v>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L284" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M284" t="n">
+        <v>0.8172590796499293</v>
+      </c>
+      <c r="N284" t="n">
+        <v>4.092960526347989</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="inlineStr">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>supp_rec90</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C285" t="n">
+        <v>430</v>
+      </c>
+      <c r="D285" t="n">
+        <v>4.724497885835096</v>
+      </c>
+      <c r="E285" t="n">
+        <v>16.01195921085962</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0.3411048413519033</v>
+      </c>
+      <c r="G285" t="n">
+        <v>450</v>
+      </c>
+      <c r="H285" t="n">
+        <v>210</v>
+      </c>
+      <c r="I285" t="n">
+        <v>30</v>
+      </c>
+      <c r="J285" t="n">
+        <v>6.576973172647285</v>
+      </c>
+      <c r="K285" t="inlineStr">
         <is>
           <t>Fe optimum</t>
         </is>
+      </c>
+      <c r="L285" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M285" t="n">
+        <v>0.720254534238471</v>
+      </c>
+      <c r="N285" t="n">
+        <v>3.644374547562157</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>source: figures/composite/fig2/fig2_pressure_envelopes.csv</t>
-        </is>
+          <t>supp_rec90</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C286" t="n">
+        <v>490</v>
+      </c>
+      <c r="D286" t="n">
+        <v>4.145987940630798</v>
+      </c>
+      <c r="E286" t="n">
+        <v>15.96220113028502</v>
+      </c>
+      <c r="F286" t="n">
+        <v>0.2913467607773103</v>
+      </c>
+      <c r="G286" t="n">
+        <v>450</v>
+      </c>
+      <c r="H286" t="n">
+        <v>205</v>
+      </c>
+      <c r="I286" t="n">
+        <v>30</v>
+      </c>
+      <c r="J286" t="n">
+        <v>6.464423217390839</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L286" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M286" t="n">
+        <v>0.670496453663878</v>
+      </c>
+      <c r="N286" t="n">
+        <v>3.425792152121148</v>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B287" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>supp_rec90</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C287" t="n">
+        <v>550</v>
+      </c>
+      <c r="D287" t="n">
+        <v>3.693698347107438</v>
+      </c>
+      <c r="E287" t="n">
+        <v>15.92198027412037</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0.2511259046126586</v>
+      </c>
+      <c r="G287" t="n">
+        <v>450</v>
+      </c>
+      <c r="H287" t="n">
+        <v>205</v>
+      </c>
+      <c r="I287" t="n">
+        <v>30</v>
+      </c>
+      <c r="J287" t="n">
+        <v>5.759213411857292</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L287" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M287" t="n">
+        <v>0.6302755974992262</v>
+      </c>
+      <c r="N287" t="n">
+        <v>3.255061413682528</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
+          <t>supp_rec90</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C288" t="n">
+        <v>430</v>
+      </c>
+      <c r="D288" t="n">
+        <v>3.779598308668076</v>
+      </c>
+      <c r="E288" t="n">
+        <v>15.92961609809863</v>
+      </c>
+      <c r="F288" t="n">
+        <v>0.2587617285909189</v>
+      </c>
+      <c r="G288" t="n">
+        <v>450</v>
+      </c>
+      <c r="H288" t="n">
+        <v>205</v>
+      </c>
+      <c r="I288" t="n">
+        <v>30</v>
+      </c>
+      <c r="J288" t="n">
+        <v>5.893148607481879</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L288" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M288" t="n">
+        <v>0.6379114214774866</v>
+      </c>
+      <c r="N288" t="n">
+        <v>3.287476389409658</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>supp_rec90</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C289" t="n">
+        <v>490</v>
+      </c>
+      <c r="D289" t="n">
+        <v>3.316790352504638</v>
+      </c>
+      <c r="E289" t="n">
+        <v>15.88847864454254</v>
+      </c>
+      <c r="F289" t="n">
+        <v>0.217624275034824</v>
+      </c>
+      <c r="G289" t="n">
+        <v>450</v>
+      </c>
+      <c r="H289" t="n">
+        <v>205</v>
+      </c>
+      <c r="I289" t="n">
+        <v>30</v>
+      </c>
+      <c r="J289" t="n">
+        <v>5.17153857391267</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L289" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M289" t="n">
+        <v>0.5967739679213917</v>
+      </c>
+      <c r="N289" t="n">
+        <v>3.112887260076322</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>supp_rec90</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C290" t="n">
+        <v>550</v>
+      </c>
+      <c r="D290" t="n">
+        <v>2.95495867768595</v>
+      </c>
+      <c r="E290" t="n">
+        <v>15.8562930053336</v>
+      </c>
+      <c r="F290" t="n">
+        <v>0.1854386358258928</v>
+      </c>
+      <c r="G290" t="n">
+        <v>450</v>
+      </c>
+      <c r="H290" t="n">
+        <v>205</v>
+      </c>
+      <c r="I290" t="n">
+        <v>30</v>
+      </c>
+      <c r="J290" t="n">
+        <v>4.607370729485834</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L290" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M290" t="n">
+        <v>0.5645883287124605</v>
+      </c>
+      <c r="N290" t="n">
+        <v>2.976471323866593</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>supp_rec97</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C291" t="n">
+        <v>430</v>
+      </c>
+      <c r="D291" t="n">
+        <v>7.559196617336151</v>
+      </c>
+      <c r="E291" t="n">
+        <v>15.99402504127174</v>
+      </c>
+      <c r="F291" t="n">
+        <v>0.7566463090105859</v>
+      </c>
+      <c r="G291" t="n">
+        <v>450</v>
+      </c>
+      <c r="H291" t="n">
+        <v>205</v>
+      </c>
+      <c r="I291" t="n">
+        <v>30</v>
+      </c>
+      <c r="J291" t="n">
+        <v>11.78629721496376</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L291" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M291" t="n">
+        <v>0.7023203646505998</v>
+      </c>
+      <c r="N291" t="n">
+        <v>3.432573323178897</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>supp_rec97</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C292" t="n">
+        <v>490</v>
+      </c>
+      <c r="D292" t="n">
+        <v>6.633580705009276</v>
+      </c>
+      <c r="E292" t="n">
+        <v>15.90981177709279</v>
+      </c>
+      <c r="F292" t="n">
+        <v>0.672433044831628</v>
+      </c>
+      <c r="G292" t="n">
+        <v>450</v>
+      </c>
+      <c r="H292" t="n">
+        <v>205</v>
+      </c>
+      <c r="I292" t="n">
+        <v>30</v>
+      </c>
+      <c r="J292" t="n">
+        <v>10.34307714782534</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L292" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M292" t="n">
+        <v>0.6181071004716419</v>
+      </c>
+      <c r="N292" t="n">
+        <v>3.079150848544201</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>supp_rec97</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C293" t="n">
+        <v>550</v>
+      </c>
+      <c r="D293" t="n">
+        <v>5.909917355371901</v>
+      </c>
+      <c r="E293" t="n">
+        <v>15.84447001740661</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0.6070912851454491</v>
+      </c>
+      <c r="G293" t="n">
+        <v>450</v>
+      </c>
+      <c r="H293" t="n">
+        <v>205</v>
+      </c>
+      <c r="I293" t="n">
+        <v>30</v>
+      </c>
+      <c r="J293" t="n">
+        <v>9.214741458971668</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L293" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M293" t="n">
+        <v>0.5527653407854629</v>
+      </c>
+      <c r="N293" t="n">
+        <v>2.802927264240084</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>supp_rec97</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C294" t="n">
+        <v>430</v>
+      </c>
+      <c r="D294" t="n">
+        <v>4.724497885835096</v>
+      </c>
+      <c r="E294" t="n">
+        <v>15.7274305403289</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0.4900518080677383</v>
+      </c>
+      <c r="G294" t="n">
+        <v>450</v>
+      </c>
+      <c r="H294" t="n">
+        <v>200</v>
+      </c>
+      <c r="I294" t="n">
+        <v>30</v>
+      </c>
+      <c r="J294" t="n">
+        <v>8.29946405323688</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L294" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M294" t="n">
+        <v>0.4357258637077521</v>
+      </c>
+      <c r="N294" t="n">
+        <v>2.35069492099115</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>supp_rec97</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C295" t="n">
+        <v>490</v>
+      </c>
+      <c r="D295" t="n">
+        <v>4.145987940630798</v>
+      </c>
+      <c r="E295" t="n">
+        <v>15.67072094226977</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0.4333422100086164</v>
+      </c>
+      <c r="G295" t="n">
+        <v>450</v>
+      </c>
+      <c r="H295" t="n">
+        <v>200</v>
+      </c>
+      <c r="I295" t="n">
+        <v>30</v>
+      </c>
+      <c r="J295" t="n">
+        <v>7.283203148758895</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L295" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M295" t="n">
+        <v>0.3790162656486302</v>
+      </c>
+      <c r="N295" t="n">
+        <v>2.130154325796559</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>supp_rec97</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C296" t="n">
+        <v>550</v>
+      </c>
+      <c r="D296" t="n">
+        <v>3.693698347107438</v>
+      </c>
+      <c r="E296" t="n">
+        <v>15.62652781444371</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0.3891490821825538</v>
+      </c>
+      <c r="G296" t="n">
+        <v>450</v>
+      </c>
+      <c r="H296" t="n">
+        <v>200</v>
+      </c>
+      <c r="I296" t="n">
+        <v>30</v>
+      </c>
+      <c r="J296" t="n">
+        <v>6.488671896167015</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L296" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M296" t="n">
+        <v>0.3348231378225677</v>
+      </c>
+      <c r="N296" t="n">
+        <v>1.957834421394614</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>supp_rec97</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C297" t="n">
+        <v>430</v>
+      </c>
+      <c r="D297" t="n">
+        <v>3.779598308668076</v>
+      </c>
+      <c r="E297" t="n">
+        <v>15.63491357279663</v>
+      </c>
+      <c r="F297" t="n">
+        <v>0.3975348405354744</v>
+      </c>
+      <c r="G297" t="n">
+        <v>450</v>
+      </c>
+      <c r="H297" t="n">
+        <v>200</v>
+      </c>
+      <c r="I297" t="n">
+        <v>30</v>
+      </c>
+      <c r="J297" t="n">
+        <v>6.639571242589503</v>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L297" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M297" t="n">
+        <v>0.3432088961754882</v>
+      </c>
+      <c r="N297" t="n">
+        <v>1.990553698912876</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>supp_rec97</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C298" t="n">
+        <v>490</v>
+      </c>
+      <c r="D298" t="n">
+        <v>3.316790352504638</v>
+      </c>
+      <c r="E298" t="n">
+        <v>15.58620003009364</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0.3488212978324849</v>
+      </c>
+      <c r="G298" t="n">
+        <v>450</v>
+      </c>
+      <c r="H298" t="n">
+        <v>195</v>
+      </c>
+      <c r="I298" t="n">
+        <v>30</v>
+      </c>
+      <c r="J298" t="n">
+        <v>6.609105545549926</v>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L298" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M298" t="n">
+        <v>0.2944953534724988</v>
+      </c>
+      <c r="N298" t="n">
+        <v>1.814322884761278</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>supp_rec97</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C299" t="n">
+        <v>550</v>
+      </c>
+      <c r="D299" t="n">
+        <v>2.95495867768595</v>
+      </c>
+      <c r="E299" t="n">
+        <v>15.54723595089578</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0.3098572186346224</v>
+      </c>
+      <c r="G299" t="n">
+        <v>450</v>
+      </c>
+      <c r="H299" t="n">
+        <v>195</v>
+      </c>
+      <c r="I299" t="n">
+        <v>30</v>
+      </c>
+      <c r="J299" t="n">
+        <v>5.888112213308116</v>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+      <c r="L299" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="M299" t="n">
+        <v>0.2555312742746363</v>
+      </c>
+      <c r="N299" t="n">
+        <v>1.676646655318585</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>kaap90</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C300" t="n">
+        <v>430</v>
+      </c>
+      <c r="D300" t="n">
+        <v>7.559196617336151</v>
+      </c>
+      <c r="E300" t="n">
+        <v>19.2036543749341</v>
+      </c>
+      <c r="F300" t="n">
+        <v>0.293255343201583</v>
+      </c>
+      <c r="G300" t="n">
+        <v>425</v>
+      </c>
+      <c r="H300" t="n">
+        <v>90</v>
+      </c>
+      <c r="I300" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J300" t="n">
+        <v>13.2159700515131</v>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L300" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M300" t="n">
+        <v>0.1349657630407819</v>
+      </c>
+      <c r="N300" t="n">
+        <v>1.211050516258996</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>kaap90</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C301" t="n">
+        <v>490</v>
+      </c>
+      <c r="D301" t="n">
+        <v>6.633580705009276</v>
+      </c>
+      <c r="E301" t="n">
+        <v>19.16281832625618</v>
+      </c>
+      <c r="F301" t="n">
+        <v>0.2524192945236549</v>
+      </c>
+      <c r="G301" t="n">
+        <v>425</v>
+      </c>
+      <c r="H301" t="n">
+        <v>90</v>
+      </c>
+      <c r="I301" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J301" t="n">
+        <v>11.59768800438905</v>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L301" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M301" t="n">
+        <v>0.09412971436285381</v>
+      </c>
+      <c r="N301" t="n">
+        <v>1.1474003127568</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>kaap90</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C302" t="n">
+        <v>550</v>
+      </c>
+      <c r="D302" t="n">
+        <v>5.909917355371901</v>
+      </c>
+      <c r="E302" t="n">
+        <v>19.13101796082532</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0.2206189290928009</v>
+      </c>
+      <c r="G302" t="n">
+        <v>425</v>
+      </c>
+      <c r="H302" t="n">
+        <v>90</v>
+      </c>
+      <c r="I302" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J302" t="n">
+        <v>10.33248567663752</v>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L302" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M302" t="n">
+        <v>0.0623293489319998</v>
+      </c>
+      <c r="N302" t="n">
+        <v>1.097673390402009</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>kaap90</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C303" t="n">
+        <v>430</v>
+      </c>
+      <c r="D303" t="n">
+        <v>4.724497885835096</v>
+      </c>
+      <c r="E303" t="n">
+        <v>19.07905355750431</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0.1686545257717888</v>
+      </c>
+      <c r="G303" t="n">
+        <v>425</v>
+      </c>
+      <c r="H303" t="n">
+        <v>90</v>
+      </c>
+      <c r="I303" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J303" t="n">
+        <v>8.259981282195689</v>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L303" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M303" t="n">
+        <v>0.0103649456109877</v>
+      </c>
+      <c r="N303" t="n">
+        <v>1.016246047228793</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>kaap90</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C304" t="n">
+        <v>490</v>
+      </c>
+      <c r="D304" t="n">
+        <v>4.145987940630798</v>
+      </c>
+      <c r="E304" t="n">
+        <v>19.05368116000772</v>
+      </c>
+      <c r="F304" t="n">
+        <v>0.143282128275203</v>
+      </c>
+      <c r="G304" t="n">
+        <v>425</v>
+      </c>
+      <c r="H304" t="n">
+        <v>90</v>
+      </c>
+      <c r="I304" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J304" t="n">
+        <v>7.248555002743156</v>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L304" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M304" t="n">
+        <v>-0.015007451885598</v>
+      </c>
+      <c r="N304" t="n">
+        <v>0.9764879597280476</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>kaap90</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C305" t="n">
+        <v>550</v>
+      </c>
+      <c r="D305" t="n">
+        <v>3.693698347107438</v>
+      </c>
+      <c r="E305" t="n">
+        <v>19.03379480349068</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0.1233957717581617</v>
+      </c>
+      <c r="G305" t="n">
+        <v>425</v>
+      </c>
+      <c r="H305" t="n">
+        <v>90</v>
+      </c>
+      <c r="I305" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J305" t="n">
+        <v>6.457803547898448</v>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L305" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M305" t="n">
+        <v>-0.0348938084026393</v>
+      </c>
+      <c r="N305" t="n">
+        <v>0.9453698241169411</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>kaap90</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C306" t="n">
+        <v>430</v>
+      </c>
+      <c r="D306" t="n">
+        <v>3.779598308668076</v>
+      </c>
+      <c r="E306" t="n">
+        <v>19.03757678725126</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0.127177755518737</v>
+      </c>
+      <c r="G306" t="n">
+        <v>425</v>
+      </c>
+      <c r="H306" t="n">
+        <v>90</v>
+      </c>
+      <c r="I306" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J306" t="n">
+        <v>6.60798502575655</v>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L306" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M306" t="n">
+        <v>-0.031111824642064</v>
+      </c>
+      <c r="N306" t="n">
+        <v>0.9512833365388436</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>kaap90</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C307" t="n">
+        <v>490</v>
+      </c>
+      <c r="D307" t="n">
+        <v>3.316790352504638</v>
+      </c>
+      <c r="E307" t="n">
+        <v>19.01716102600268</v>
+      </c>
+      <c r="F307" t="n">
+        <v>0.1067619942701547</v>
+      </c>
+      <c r="G307" t="n">
+        <v>425</v>
+      </c>
+      <c r="H307" t="n">
+        <v>90</v>
+      </c>
+      <c r="I307" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J307" t="n">
+        <v>5.798844002194524</v>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L307" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M307" t="n">
+        <v>-0.0515275858906463</v>
+      </c>
+      <c r="N307" t="n">
+        <v>0.9193957377774196</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>kaap90</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C308" t="n">
+        <v>550</v>
+      </c>
+      <c r="D308" t="n">
+        <v>2.95495867768595</v>
+      </c>
+      <c r="E308" t="n">
+        <v>19.00111109653497</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0.0907120648024495</v>
+      </c>
+      <c r="G308" t="n">
+        <v>425</v>
+      </c>
+      <c r="H308" t="n">
+        <v>90</v>
+      </c>
+      <c r="I308" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J308" t="n">
+        <v>5.166242838318758</v>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L308" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M308" t="n">
+        <v>-0.06757751535835151</v>
+      </c>
+      <c r="N308" t="n">
+        <v>0.8944032116822221</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>kaap97</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C309" t="n">
+        <v>430</v>
+      </c>
+      <c r="D309" t="n">
+        <v>7.559196617336151</v>
+      </c>
+      <c r="E309" t="n">
+        <v>18.89474936961769</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0.7377578220652765</v>
+      </c>
+      <c r="G309" t="n">
+        <v>425</v>
+      </c>
+      <c r="H309" t="n">
+        <v>90</v>
+      </c>
+      <c r="I309" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J309" t="n">
+        <v>13.2159700515131</v>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L309" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M309" t="n">
+        <v>-0.1739392422756296</v>
+      </c>
+      <c r="N309" t="n">
+        <v>0.7298807192144522</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>kaap97</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C310" t="n">
+        <v>490</v>
+      </c>
+      <c r="D310" t="n">
+        <v>6.633580705009276</v>
+      </c>
+      <c r="E310" t="n">
+        <v>18.85391332093976</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0.6969217733873485</v>
+      </c>
+      <c r="G310" t="n">
+        <v>425</v>
+      </c>
+      <c r="H310" t="n">
+        <v>90</v>
+      </c>
+      <c r="I310" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J310" t="n">
+        <v>11.59768800438905</v>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L310" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M310" t="n">
+        <v>-0.2147752909535576</v>
+      </c>
+      <c r="N310" t="n">
+        <v>0.6655218856676183</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>kaap97</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C311" t="n">
+        <v>550</v>
+      </c>
+      <c r="D311" t="n">
+        <v>5.909917355371901</v>
+      </c>
+      <c r="E311" t="n">
+        <v>18.7795133476303</v>
+      </c>
+      <c r="F311" t="n">
+        <v>0.6225218000778909</v>
+      </c>
+      <c r="G311" t="n">
+        <v>400</v>
+      </c>
+      <c r="H311" t="n">
+        <v>90</v>
+      </c>
+      <c r="I311" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J311" t="n">
+        <v>29.00156996896854</v>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L311" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M311" t="n">
+        <v>-0.2891752642630152</v>
+      </c>
+      <c r="N311" t="n">
+        <v>0.6152497793062117</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>kaap97</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C312" t="n">
+        <v>430</v>
+      </c>
+      <c r="D312" t="n">
+        <v>4.724497885835096</v>
+      </c>
+      <c r="E312" t="n">
+        <v>18.6236793131958</v>
+      </c>
+      <c r="F312" t="n">
+        <v>0.4666877656433819</v>
+      </c>
+      <c r="G312" t="n">
+        <v>400</v>
+      </c>
+      <c r="H312" t="n">
+        <v>90</v>
+      </c>
+      <c r="I312" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J312" t="n">
+        <v>23.18439459728591</v>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L312" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M312" t="n">
+        <v>-0.4450092986975242</v>
+      </c>
+      <c r="N312" t="n">
+        <v>0.5330136947337196</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>kaap97</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C313" t="n">
+        <v>490</v>
+      </c>
+      <c r="D313" t="n">
+        <v>4.145987940630798</v>
+      </c>
+      <c r="E313" t="n">
+        <v>18.54915532215126</v>
+      </c>
+      <c r="F313" t="n">
+        <v>0.3921637745988455</v>
+      </c>
+      <c r="G313" t="n">
+        <v>400</v>
+      </c>
+      <c r="H313" t="n">
+        <v>90</v>
+      </c>
+      <c r="I313" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J313" t="n">
+        <v>20.34548913639375</v>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L313" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M313" t="n">
+        <v>-0.5195332897420606</v>
+      </c>
+      <c r="N313" t="n">
+        <v>0.4929477104905125</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>kaap97</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C314" t="n">
+        <v>550</v>
+      </c>
+      <c r="D314" t="n">
+        <v>3.693698347107438</v>
+      </c>
+      <c r="E314" t="n">
+        <v>18.49156970316873</v>
+      </c>
+      <c r="F314" t="n">
+        <v>0.3345781556163132</v>
+      </c>
+      <c r="G314" t="n">
+        <v>400</v>
+      </c>
+      <c r="H314" t="n">
+        <v>90</v>
+      </c>
+      <c r="I314" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J314" t="n">
+        <v>18.12598123060534</v>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L314" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M314" t="n">
+        <v>-0.5771189087245929</v>
+      </c>
+      <c r="N314" t="n">
+        <v>0.4616622970592647</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>kaap97</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C315" t="n">
+        <v>430</v>
+      </c>
+      <c r="D315" t="n">
+        <v>3.779598308668076</v>
+      </c>
+      <c r="E315" t="n">
+        <v>18.50246176367698</v>
+      </c>
+      <c r="F315" t="n">
+        <v>0.3454702161245642</v>
+      </c>
+      <c r="G315" t="n">
+        <v>400</v>
+      </c>
+      <c r="H315" t="n">
+        <v>90</v>
+      </c>
+      <c r="I315" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J315" t="n">
+        <v>18.54751567782872</v>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L315" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M315" t="n">
+        <v>-0.5662268482163419</v>
+      </c>
+      <c r="N315" t="n">
+        <v>0.4676011929907497</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>kaap97</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C316" t="n">
+        <v>490</v>
+      </c>
+      <c r="D316" t="n">
+        <v>3.316790352504638</v>
+      </c>
+      <c r="E316" t="n">
+        <v>18.444018008323</v>
+      </c>
+      <c r="F316" t="n">
+        <v>0.2870264607705799</v>
+      </c>
+      <c r="G316" t="n">
+        <v>400</v>
+      </c>
+      <c r="H316" t="n">
+        <v>90</v>
+      </c>
+      <c r="I316" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J316" t="n">
+        <v>16.276391309115</v>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L316" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M316" t="n">
+        <v>-0.6246706035703262</v>
+      </c>
+      <c r="N316" t="n">
+        <v>0.4356214629163839</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>kaap97</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C317" t="n">
+        <v>550</v>
+      </c>
+      <c r="D317" t="n">
+        <v>2.95495867768595</v>
+      </c>
+      <c r="E317" t="n">
+        <v>18.39871863363259</v>
+      </c>
+      <c r="F317" t="n">
+        <v>0.241727086080175</v>
+      </c>
+      <c r="G317" t="n">
+        <v>400</v>
+      </c>
+      <c r="H317" t="n">
+        <v>90</v>
+      </c>
+      <c r="I317" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J317" t="n">
+        <v>14.50078498448427</v>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Fe in the KAAP loop</t>
+        </is>
+      </c>
+      <c r="L317" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="M317" t="n">
+        <v>-0.6699699782607311</v>
+      </c>
+      <c r="N317" t="n">
+        <v>0.4106514740290691</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>source: figures/composite/fig2/fig2_pressure_envelopes.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B322" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
           <t>Fe cost USD/t</t>
         </is>
       </c>
-      <c r="B288" t="n">
+      <c r="B323" t="n">
         <v>15.29170467662114</v>
       </c>
     </row>

--- a/source_data/SourceData_Fig3.xlsx
+++ b/source_data/SourceData_Fig3.xlsx
@@ -18425,7 +18425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N323"/>
+  <dimension ref="A1:O323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22026,6 +22026,16 @@
           <t>metal_cost</t>
         </is>
       </c>
+      <c r="N258" s="1" t="inlineStr">
+        <is>
+          <t>Fe_same_loop_cost</t>
+        </is>
+      </c>
+      <c r="O258" s="1" t="inlineStr">
+        <is>
+          <t>gap_to_Fe_same_loop</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -22048,13 +22058,13 @@
         <v>53852.5</v>
       </c>
       <c r="F259" t="n">
-        <v>22.03059478781103</v>
+        <v>22.03059478781101</v>
       </c>
       <c r="G259" t="n">
-        <v>6.738890111189885</v>
+        <v>6.738890111189868</v>
       </c>
       <c r="H259" t="n">
-        <v>201.2234429879013</v>
+        <v>201.2234429878986</v>
       </c>
       <c r="I259" t="n">
         <v>450</v>
@@ -22066,10 +22076,16 @@
         <v>25</v>
       </c>
       <c r="L259" t="n">
-        <v>0.0660321094260847</v>
+        <v>0.0660321094260842</v>
       </c>
       <c r="M259" t="n">
-        <v>1.833375222075033</v>
+        <v>1.833375222075018</v>
+      </c>
+      <c r="N259" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="O259" t="n">
+        <v>6.738890111189868</v>
       </c>
     </row>
     <row r="260">
@@ -22093,13 +22109,13 @@
         <v>4895.681818181818</v>
       </c>
       <c r="F260" t="n">
-        <v>17.9499692560481</v>
+        <v>17.94996925604808</v>
       </c>
       <c r="G260" t="n">
-        <v>2.658264579426952</v>
+        <v>2.658264579426937</v>
       </c>
       <c r="H260" t="n">
-        <v>18.48410396774704</v>
+        <v>18.48410396774684</v>
       </c>
       <c r="I260" t="n">
         <v>450</v>
@@ -22111,10 +22127,16 @@
         <v>20</v>
       </c>
       <c r="L260" t="n">
-        <v>0.5319674845939432</v>
+        <v>0.5319674845939377</v>
       </c>
       <c r="M260" t="n">
-        <v>1.342729680620343</v>
+        <v>1.342729680620329</v>
+      </c>
+      <c r="N260" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="O260" t="n">
+        <v>2.658264579426937</v>
       </c>
     </row>
     <row r="261">
@@ -22138,13 +22160,13 @@
         <v>489.5681818181818</v>
       </c>
       <c r="F261" t="n">
-        <v>15.67085436950771</v>
+        <v>15.6708543695077</v>
       </c>
       <c r="G261" t="n">
-        <v>0.3791496928865676</v>
+        <v>0.3791496928865552</v>
       </c>
       <c r="H261" t="n">
-        <v>2.234218129677338</v>
+        <v>2.234218129677315</v>
       </c>
       <c r="I261" t="n">
         <v>450</v>
@@ -22156,10 +22178,16 @@
         <v>30</v>
       </c>
       <c r="L261" t="n">
-        <v>1.756687007548503</v>
+        <v>1.756687007548483</v>
       </c>
       <c r="M261" t="n">
-        <v>0.443402247864072</v>
+        <v>0.4434022478640671</v>
+      </c>
+      <c r="N261" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0.3791496928865552</v>
       </c>
     </row>
     <row r="262">
@@ -22183,13 +22211,13 @@
         <v>146.8704545454547</v>
       </c>
       <c r="F262" t="n">
-        <v>15.23737873226116</v>
+        <v>15.23737873226115</v>
       </c>
       <c r="G262" t="n">
-        <v>-0.0543259443599861</v>
+        <v>-0.0543259443599968</v>
       </c>
       <c r="H262" t="n">
-        <v>0.9357377150328882</v>
+        <v>0.9357377150328752</v>
       </c>
       <c r="I262" t="n">
         <v>425</v>
@@ -22201,10 +22229,16 @@
         <v>30</v>
       </c>
       <c r="L262" t="n">
-        <v>6.237550738484852</v>
+        <v>6.237550738484763</v>
       </c>
       <c r="M262" t="n">
-        <v>0.4723227313788896</v>
+        <v>0.4723227313788828</v>
+      </c>
+      <c r="N262" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="O262" t="n">
+        <v>-0.0543259443599968</v>
       </c>
     </row>
     <row r="263">
@@ -22231,7 +22265,7 @@
         <v>18.91039903173252</v>
       </c>
       <c r="G263" t="n">
-        <v>3.618694355111376</v>
+        <v>3.618694355111369</v>
       </c>
       <c r="H263" t="n">
         <v/>
@@ -22246,10 +22280,16 @@
         <v>-20</v>
       </c>
       <c r="L263" t="n">
-        <v>1.748329977448104</v>
+        <v>1.748329977448083</v>
       </c>
       <c r="M263" t="n">
-        <v>0.4412928647377318</v>
+        <v>0.4412928647377263</v>
+      </c>
+      <c r="N263" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="O263" t="n">
+        <v>-0.1582895801608081</v>
       </c>
     </row>
     <row r="264">
@@ -22273,10 +22313,10 @@
         <v>146.8704545454547</v>
       </c>
       <c r="F264" t="n">
-        <v>18.15699154755242</v>
+        <v>18.15699154755241</v>
       </c>
       <c r="G264" t="n">
-        <v>2.865286870931272</v>
+        <v>2.865286870931268</v>
       </c>
       <c r="H264" t="n">
         <v/>
@@ -22291,10 +22331,16 @@
         <v>-20</v>
       </c>
       <c r="L264" t="n">
-        <v>4.907271663047397</v>
+        <v>4.907271663047357</v>
       </c>
       <c r="M264" t="n">
-        <v>0.3715907176847731</v>
+        <v>0.3715907176847701</v>
+      </c>
+      <c r="N264" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="O264" t="n">
+        <v>-0.9116970643409096</v>
       </c>
     </row>
     <row r="265">
@@ -22333,10 +22379,16 @@
         <v>-20</v>
       </c>
       <c r="L265" t="n">
-        <v>21.64633610219298</v>
+        <v>21.64633610219303</v>
       </c>
       <c r="M265" t="n">
-        <v>0.0892821626340487</v>
+        <v>0.08928216263404889</v>
+      </c>
+      <c r="N265" t="n">
+        <v>19.06868861189332</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -22370,6 +22422,12 @@
       </c>
       <c r="L266" t="n">
         <v>4.297918560666256</v>
+      </c>
+      <c r="N266" t="n">
+        <v>15.29170467662114</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="269">

--- a/source_data/SourceData_Fig3.xlsx
+++ b/source_data/SourceData_Fig3.xlsx
@@ -22193,52 +22193,52 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>supp_rec97</t>
+          <t>supp_rec_hi</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Supported Ru/C, 97% recovery</t>
+          <t>Supported Ru/C, 95.55% recovery</t>
         </is>
       </c>
       <c r="C262" t="n">
         <v>11</v>
       </c>
       <c r="D262" t="n">
-        <v>0.97</v>
+        <v>0.9555</v>
       </c>
       <c r="E262" t="n">
-        <v>146.8704545454547</v>
+        <v>217.8578409090908</v>
       </c>
       <c r="F262" t="n">
-        <v>15.23737873226115</v>
+        <v>15.40709310418436</v>
       </c>
       <c r="G262" t="n">
-        <v>-0.0543259443599968</v>
+        <v>0.1153884275632108</v>
       </c>
       <c r="H262" t="n">
-        <v>0.9357377150328752</v>
+        <v>1.205812816786987</v>
       </c>
       <c r="I262" t="n">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="J262" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="K262" t="n">
         <v>30</v>
       </c>
       <c r="L262" t="n">
-        <v>6.237550738484763</v>
+        <v>1.992620830122429</v>
       </c>
       <c r="M262" t="n">
-        <v>0.4723227313788828</v>
+        <v>0.2238144788355164</v>
       </c>
       <c r="N262" t="n">
         <v>15.29170467662114</v>
       </c>
       <c r="O262" t="n">
-        <v>-0.0543259443599968</v>
+        <v>0.1153884275632108</v>
       </c>
     </row>
     <row r="263">
@@ -22295,28 +22295,28 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>kaap97</t>
+          <t>kaap_hi</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Supported Ru/C, 97% recovery, KAAP loop (90 bar, Tsep -20 C)</t>
+          <t>Supported Ru/C, 95.55% recovery, KAAP loop (90 bar, Tsep -20 C)</t>
         </is>
       </c>
       <c r="C264" t="n">
         <v>11</v>
       </c>
       <c r="D264" t="n">
-        <v>0.97</v>
+        <v>0.9555</v>
       </c>
       <c r="E264" t="n">
-        <v>146.8704545454547</v>
+        <v>217.8578409090908</v>
       </c>
       <c r="F264" t="n">
-        <v>18.15699154755241</v>
+        <v>18.33659372776672</v>
       </c>
       <c r="G264" t="n">
-        <v>2.865286870931268</v>
+        <v>3.044889051145574</v>
       </c>
       <c r="H264" t="n">
         <v/>
@@ -22334,13 +22334,13 @@
         <v>4.907271663047357</v>
       </c>
       <c r="M264" t="n">
-        <v>0.3715907176847701</v>
+        <v>0.551192897899075</v>
       </c>
       <c r="N264" t="n">
         <v>19.06868861189332</v>
       </c>
       <c r="O264" t="n">
-        <v>-0.9116970643409096</v>
+        <v>-0.7320948841266031</v>
       </c>
     </row>
     <row r="265">
@@ -22539,10 +22539,10 @@
         <v>7.559196617336151</v>
       </c>
       <c r="E273" t="n">
-        <v>18.17808825112052</v>
+        <v>18.1780882511205</v>
       </c>
       <c r="F273" t="n">
-        <v>0.2281189950724247</v>
+        <v>0.2281189950724211</v>
       </c>
       <c r="G273" t="n">
         <v>450</v>
@@ -22554,7 +22554,7 @@
         <v>20</v>
       </c>
       <c r="J273" t="n">
-        <v>4.021246810075357</v>
+        <v>4.021246810075315</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
@@ -22565,10 +22565,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M273" t="n">
-        <v>2.886383574499376</v>
+        <v>2.886383574499359</v>
       </c>
       <c r="N273" t="n">
-        <v>21.36770571649332</v>
+        <v>21.36770571649306</v>
       </c>
     </row>
     <row r="274">
@@ -22587,10 +22587,10 @@
         <v>6.633580705009276</v>
       </c>
       <c r="E274" t="n">
-        <v>18.1475857989463</v>
+        <v>18.14758579894628</v>
       </c>
       <c r="F274" t="n">
-        <v>0.1976165428982064</v>
+        <v>0.1976165428982028</v>
       </c>
       <c r="G274" t="n">
         <v>450</v>
@@ -22602,7 +22602,7 @@
         <v>20</v>
       </c>
       <c r="J274" t="n">
-        <v>3.528849241494701</v>
+        <v>3.528849241494665</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -22613,10 +22613,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M274" t="n">
-        <v>2.855881122325158</v>
+        <v>2.85588112232514</v>
       </c>
       <c r="N274" t="n">
-        <v>20.99255384200304</v>
+        <v>20.9925538420028</v>
       </c>
     </row>
     <row r="275">
@@ -22635,10 +22635,10 @@
         <v>5.909917355371901</v>
       </c>
       <c r="E275" t="n">
-        <v>18.12362266669823</v>
+        <v>18.12362266669821</v>
       </c>
       <c r="F275" t="n">
-        <v>0.1736534106501324</v>
+        <v>0.1736534106501288</v>
       </c>
       <c r="G275" t="n">
         <v>450</v>
@@ -22650,7 +22650,7 @@
         <v>20</v>
       </c>
       <c r="J275" t="n">
-        <v>3.143883869695279</v>
+        <v>3.143883869695247</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -22661,10 +22661,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M275" t="n">
-        <v>2.831917990077084</v>
+        <v>2.831917990077066</v>
       </c>
       <c r="N275" t="n">
-        <v>20.69614240487593</v>
+        <v>20.69614240487567</v>
       </c>
     </row>
     <row r="276">
@@ -22683,7 +22683,7 @@
         <v>4.724497885835096</v>
       </c>
       <c r="E276" t="n">
-        <v>18.08401494971733</v>
+        <v>18.08401494971732</v>
       </c>
       <c r="F276" t="n">
         <v>0.1340456936692362</v>
@@ -22698,7 +22698,7 @@
         <v>20</v>
       </c>
       <c r="J276" t="n">
-        <v>2.513279256297098</v>
+        <v>2.513279256297072</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
@@ -22709,10 +22709,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M276" t="n">
-        <v>2.792310273096188</v>
+        <v>2.792310273096174</v>
       </c>
       <c r="N276" t="n">
-        <v>20.20257682776744</v>
+        <v>20.20257682776722</v>
       </c>
     </row>
     <row r="277">
@@ -22731,7 +22731,7 @@
         <v>4.145987940630798</v>
       </c>
       <c r="E277" t="n">
-        <v>18.06444592653087</v>
+        <v>18.06444592653085</v>
       </c>
       <c r="F277" t="n">
         <v>0.1144766704827731</v>
@@ -22746,7 +22746,7 @@
         <v>20</v>
       </c>
       <c r="J277" t="n">
-        <v>2.205530775934188</v>
+        <v>2.205530775934166</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
@@ -22757,10 +22757,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M277" t="n">
-        <v>2.772741249909725</v>
+        <v>2.772741249909711</v>
       </c>
       <c r="N277" t="n">
-        <v>19.95683618142185</v>
+        <v>19.9568361814216</v>
       </c>
     </row>
     <row r="278">
@@ -22779,7 +22779,7 @@
         <v>3.693698347107438</v>
       </c>
       <c r="E278" t="n">
-        <v>18.04898887199468</v>
+        <v>18.04898887199466</v>
       </c>
       <c r="F278" t="n">
         <v>0.09901961594657741</v>
@@ -22794,7 +22794,7 @@
         <v>20</v>
       </c>
       <c r="J278" t="n">
-        <v>1.964927418559549</v>
+        <v>1.964927418559529</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -22805,10 +22805,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M278" t="n">
-        <v>2.757284195373529</v>
+        <v>2.757284195373515</v>
       </c>
       <c r="N278" t="n">
-        <v>19.76173333750837</v>
+        <v>19.76173333750813</v>
       </c>
     </row>
     <row r="279">
@@ -22827,10 +22827,10 @@
         <v>3.779598308668076</v>
       </c>
       <c r="E279" t="n">
-        <v>18.05193703319081</v>
+        <v>18.05193703319079</v>
       </c>
       <c r="F279" t="n">
-        <v>0.1019677771427112</v>
+        <v>0.1019677771427076</v>
       </c>
       <c r="G279" t="n">
         <v>450</v>
@@ -22842,7 +22842,7 @@
         <v>20</v>
       </c>
       <c r="J279" t="n">
-        <v>2.010623405037678</v>
+        <v>2.010623405037657</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -22853,10 +22853,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M279" t="n">
-        <v>2.760232356569663</v>
+        <v>2.760232356569645</v>
       </c>
       <c r="N279" t="n">
-        <v>19.79901811274726</v>
+        <v>19.79901811274701</v>
       </c>
     </row>
     <row r="280">
@@ -22875,7 +22875,7 @@
         <v>3.316790352504638</v>
       </c>
       <c r="E280" t="n">
-        <v>18.03597214409293</v>
+        <v>18.03597214409292</v>
       </c>
       <c r="F280" t="n">
         <v>0.08600288804483459</v>
@@ -22890,7 +22890,7 @@
         <v>20</v>
       </c>
       <c r="J280" t="n">
-        <v>1.76442462074735</v>
+        <v>1.764424620747332</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -22901,10 +22901,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M280" t="n">
-        <v>2.744267467471786</v>
+        <v>2.744267467471772</v>
       </c>
       <c r="N280" t="n">
-        <v>19.59668043639056</v>
+        <v>19.5966804363903</v>
       </c>
     </row>
     <row r="281">
@@ -22923,7 +22923,7 @@
         <v>2.95495867768595</v>
       </c>
       <c r="E281" t="n">
-        <v>18.02333019080553</v>
+        <v>18.02333019080552</v>
       </c>
       <c r="F281" t="n">
         <v>0.0733609347574315</v>
@@ -22938,7 +22938,7 @@
         <v>20</v>
       </c>
       <c r="J281" t="n">
-        <v>1.57194193484764</v>
+        <v>1.571941934847623</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -22949,10 +22949,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M281" t="n">
-        <v>2.731625514184384</v>
+        <v>2.731625514184369</v>
       </c>
       <c r="N281" t="n">
-        <v>19.43565716567129</v>
+        <v>19.43565716567106</v>
       </c>
     </row>
     <row r="282">
@@ -22971,10 +22971,10 @@
         <v>7.559196617336151</v>
       </c>
       <c r="E282" t="n">
-        <v>16.24160844932956</v>
+        <v>16.24160844932955</v>
       </c>
       <c r="F282" t="n">
-        <v>0.5707540798218496</v>
+        <v>0.5707540798218513</v>
       </c>
       <c r="G282" t="n">
         <v>450</v>
@@ -22986,7 +22986,7 @@
         <v>30</v>
       </c>
       <c r="J282" t="n">
-        <v>9.444383138974077</v>
+        <v>9.444383138973979</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -22997,10 +22997,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M282" t="n">
-        <v>0.9499037727084172</v>
+        <v>0.9499037727084064</v>
       </c>
       <c r="N282" t="n">
-        <v>4.718376739031267</v>
+        <v>4.718376739031196</v>
       </c>
     </row>
     <row r="283">
@@ -23019,10 +23019,10 @@
         <v>6.633580705009276</v>
       </c>
       <c r="E283" t="n">
-        <v>16.16854033282638</v>
+        <v>16.16854033282637</v>
       </c>
       <c r="F283" t="n">
-        <v>0.4976859633186699</v>
+        <v>0.4976859633186752</v>
       </c>
       <c r="G283" t="n">
         <v>450</v>
@@ -23034,7 +23034,7 @@
         <v>30</v>
       </c>
       <c r="J283" t="n">
-        <v>9.234607230165985</v>
+        <v>9.234607230165889</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -23045,10 +23045,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M283" t="n">
-        <v>0.8768356562052375</v>
+        <v>0.8768356562052304</v>
       </c>
       <c r="N283" t="n">
-        <v>4.367213315780148</v>
+        <v>4.367213315780083</v>
       </c>
     </row>
     <row r="284">
@@ -23067,10 +23067,10 @@
         <v>5.909917355371901</v>
       </c>
       <c r="E284" t="n">
-        <v>16.10896375627107</v>
+        <v>16.10896375627106</v>
       </c>
       <c r="F284" t="n">
-        <v>0.4381093867633616</v>
+        <v>0.4381093867633634</v>
       </c>
       <c r="G284" t="n">
         <v>450</v>
@@ -23082,7 +23082,7 @@
         <v>30</v>
       </c>
       <c r="J284" t="n">
-        <v>8.227195532329695</v>
+        <v>8.22719553232961</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -23093,10 +23093,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M284" t="n">
-        <v>0.8172590796499293</v>
+        <v>0.8172590796499186</v>
       </c>
       <c r="N284" t="n">
-        <v>4.092960526347989</v>
+        <v>4.092960526347931</v>
       </c>
     </row>
     <row r="285">
@@ -23115,10 +23115,10 @@
         <v>4.724497885835096</v>
       </c>
       <c r="E285" t="n">
-        <v>16.01195921085962</v>
+        <v>16.01195921085961</v>
       </c>
       <c r="F285" t="n">
-        <v>0.3411048413519033</v>
+        <v>0.3411048413519086</v>
       </c>
       <c r="G285" t="n">
         <v>450</v>
@@ -23130,7 +23130,7 @@
         <v>30</v>
       </c>
       <c r="J285" t="n">
-        <v>6.576973172647285</v>
+        <v>6.576973172647218</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -23141,10 +23141,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M285" t="n">
-        <v>0.720254534238471</v>
+        <v>0.7202545342384639</v>
       </c>
       <c r="N285" t="n">
-        <v>3.644374547562157</v>
+        <v>3.644374547562099</v>
       </c>
     </row>
     <row r="286">
@@ -23163,10 +23163,10 @@
         <v>4.145987940630798</v>
       </c>
       <c r="E286" t="n">
-        <v>15.96220113028502</v>
+        <v>15.96220113028501</v>
       </c>
       <c r="F286" t="n">
-        <v>0.2913467607773103</v>
+        <v>0.2913467607773139</v>
       </c>
       <c r="G286" t="n">
         <v>450</v>
@@ -23178,7 +23178,7 @@
         <v>30</v>
       </c>
       <c r="J286" t="n">
-        <v>6.464423217390839</v>
+        <v>6.464423217390767</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -23189,10 +23189,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M286" t="n">
-        <v>0.670496453663878</v>
+        <v>0.6704964536638691</v>
       </c>
       <c r="N286" t="n">
-        <v>3.425792152121148</v>
+        <v>3.425792152121099</v>
       </c>
     </row>
     <row r="287">
@@ -23211,10 +23211,10 @@
         <v>3.693698347107438</v>
       </c>
       <c r="E287" t="n">
-        <v>15.92198027412037</v>
+        <v>15.92198027412036</v>
       </c>
       <c r="F287" t="n">
-        <v>0.2511259046126586</v>
+        <v>0.2511259046126621</v>
       </c>
       <c r="G287" t="n">
         <v>450</v>
@@ -23226,7 +23226,7 @@
         <v>30</v>
       </c>
       <c r="J287" t="n">
-        <v>5.759213411857292</v>
+        <v>5.759213411857228</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
@@ -23237,10 +23237,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M287" t="n">
-        <v>0.6302755974992262</v>
+        <v>0.6302755974992174</v>
       </c>
       <c r="N287" t="n">
-        <v>3.255061413682528</v>
+        <v>3.255061413682482</v>
       </c>
     </row>
     <row r="288">
@@ -23259,10 +23259,10 @@
         <v>3.779598308668076</v>
       </c>
       <c r="E288" t="n">
-        <v>15.92961609809863</v>
+        <v>15.92961609809862</v>
       </c>
       <c r="F288" t="n">
-        <v>0.2587617285909189</v>
+        <v>0.2587617285909243</v>
       </c>
       <c r="G288" t="n">
         <v>450</v>
@@ -23274,7 +23274,7 @@
         <v>30</v>
       </c>
       <c r="J288" t="n">
-        <v>5.893148607481879</v>
+        <v>5.893148607481814</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
@@ -23285,10 +23285,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M288" t="n">
-        <v>0.6379114214774866</v>
+        <v>0.6379114214774795</v>
       </c>
       <c r="N288" t="n">
-        <v>3.287476389409658</v>
+        <v>3.287476389409615</v>
       </c>
     </row>
     <row r="289">
@@ -23307,10 +23307,10 @@
         <v>3.316790352504638</v>
       </c>
       <c r="E289" t="n">
-        <v>15.88847864454254</v>
+        <v>15.88847864454253</v>
       </c>
       <c r="F289" t="n">
-        <v>0.217624275034824</v>
+        <v>0.2176242750348294</v>
       </c>
       <c r="G289" t="n">
         <v>450</v>
@@ -23322,7 +23322,7 @@
         <v>30</v>
       </c>
       <c r="J289" t="n">
-        <v>5.17153857391267</v>
+        <v>5.171538573912613</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
@@ -23333,10 +23333,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M289" t="n">
-        <v>0.5967739679213917</v>
+        <v>0.5967739679213846</v>
       </c>
       <c r="N289" t="n">
-        <v>3.112887260076322</v>
+        <v>3.112887260076273</v>
       </c>
     </row>
     <row r="290">
@@ -23358,7 +23358,7 @@
         <v>15.8562930053336</v>
       </c>
       <c r="F290" t="n">
-        <v>0.1854386358258928</v>
+        <v>0.1854386358258981</v>
       </c>
       <c r="G290" t="n">
         <v>450</v>
@@ -23370,7 +23370,7 @@
         <v>30</v>
       </c>
       <c r="J290" t="n">
-        <v>4.607370729485834</v>
+        <v>4.607370729485782</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -23381,16 +23381,16 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M290" t="n">
-        <v>0.5645883287124605</v>
+        <v>0.5645883287124533</v>
       </c>
       <c r="N290" t="n">
-        <v>2.976471323866593</v>
+        <v>2.976471323866549</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>supp_rec97</t>
+          <t>supp_rec_hi</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -23403,22 +23403,22 @@
         <v>7.559196617336151</v>
       </c>
       <c r="E291" t="n">
-        <v>15.99402504127174</v>
+        <v>16.05021241195982</v>
       </c>
       <c r="F291" t="n">
-        <v>0.7566463090105859</v>
+        <v>0.6431193077754678</v>
       </c>
       <c r="G291" t="n">
         <v>450</v>
       </c>
       <c r="H291" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="I291" t="n">
         <v>30</v>
       </c>
       <c r="J291" t="n">
-        <v>11.78629721496376</v>
+        <v>10.52315707623555</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -23429,16 +23429,16 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M291" t="n">
-        <v>0.7023203646505998</v>
+        <v>0.7585077353386787</v>
       </c>
       <c r="N291" t="n">
-        <v>3.432573323178897</v>
+        <v>3.697081554801237</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>supp_rec97</t>
+          <t>supp_rec_hi</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -23451,10 +23451,10 @@
         <v>6.633580705009276</v>
       </c>
       <c r="E292" t="n">
-        <v>15.90981177709279</v>
+        <v>15.9668772276154</v>
       </c>
       <c r="F292" t="n">
-        <v>0.672433044831628</v>
+        <v>0.5597841234310419</v>
       </c>
       <c r="G292" t="n">
         <v>450</v>
@@ -23466,7 +23466,7 @@
         <v>30</v>
       </c>
       <c r="J292" t="n">
-        <v>10.34307714782534</v>
+        <v>10.34307714782522</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -23477,16 +23477,16 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M292" t="n">
-        <v>0.6181071004716419</v>
+        <v>0.6751725509942528</v>
       </c>
       <c r="N292" t="n">
-        <v>3.079150848544201</v>
+        <v>3.344101892557686</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>supp_rec97</t>
+          <t>supp_rec_hi</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -23499,10 +23499,10 @@
         <v>5.909917355371901</v>
       </c>
       <c r="E293" t="n">
-        <v>15.84447001740661</v>
+        <v>15.90153546792922</v>
       </c>
       <c r="F293" t="n">
-        <v>0.6070912851454491</v>
+        <v>0.4944423637448629</v>
       </c>
       <c r="G293" t="n">
         <v>450</v>
@@ -23514,7 +23514,7 @@
         <v>30</v>
       </c>
       <c r="J293" t="n">
-        <v>9.214741458971668</v>
+        <v>9.214741458971565</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -23525,16 +23525,16 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M293" t="n">
-        <v>0.5527653407854629</v>
+        <v>0.6098307913080738</v>
       </c>
       <c r="N293" t="n">
-        <v>2.802927264240084</v>
+        <v>3.068286244591213</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>supp_rec97</t>
+          <t>supp_rec_hi</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -23547,10 +23547,10 @@
         <v>4.724497885835096</v>
       </c>
       <c r="E294" t="n">
-        <v>15.7274305403289</v>
+        <v>15.79172386626917</v>
       </c>
       <c r="F294" t="n">
-        <v>0.4900518080677383</v>
+        <v>0.3846307620848161</v>
       </c>
       <c r="G294" t="n">
         <v>450</v>
@@ -23562,7 +23562,7 @@
         <v>30</v>
       </c>
       <c r="J294" t="n">
-        <v>8.29946405323688</v>
+        <v>8.299464053236786</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -23573,16 +23573,16 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M294" t="n">
-        <v>0.4357258637077521</v>
+        <v>0.5000191896480271</v>
       </c>
       <c r="N294" t="n">
-        <v>2.35069492099115</v>
+        <v>2.616875740322472</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>supp_rec97</t>
+          <t>supp_rec_hi</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -23595,10 +23595,10 @@
         <v>4.145987940630798</v>
       </c>
       <c r="E295" t="n">
-        <v>15.67072094226977</v>
+        <v>15.73501426821005</v>
       </c>
       <c r="F295" t="n">
-        <v>0.4333422100086164</v>
+        <v>0.327921164025696</v>
       </c>
       <c r="G295" t="n">
         <v>450</v>
@@ -23610,7 +23610,7 @@
         <v>30</v>
       </c>
       <c r="J295" t="n">
-        <v>7.283203148758895</v>
+        <v>7.283203148758813</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -23621,16 +23621,16 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M295" t="n">
-        <v>0.3790162656486302</v>
+        <v>0.4433095915889069</v>
       </c>
       <c r="N295" t="n">
-        <v>2.130154325796559</v>
+        <v>2.396823968939847</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>supp_rec97</t>
+          <t>supp_rec_hi</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -23643,10 +23643,10 @@
         <v>3.693698347107438</v>
       </c>
       <c r="E296" t="n">
-        <v>15.62652781444371</v>
+        <v>15.69082114038399</v>
       </c>
       <c r="F296" t="n">
-        <v>0.3891490821825538</v>
+        <v>0.2837280361996335</v>
       </c>
       <c r="G296" t="n">
         <v>450</v>
@@ -23658,7 +23658,7 @@
         <v>30</v>
       </c>
       <c r="J296" t="n">
-        <v>6.488671896167015</v>
+        <v>6.488671896166942</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -23669,16 +23669,16 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M296" t="n">
-        <v>0.3348231378225677</v>
+        <v>0.3991164637628444</v>
       </c>
       <c r="N296" t="n">
-        <v>1.957834421394614</v>
+        <v>2.224934880216945</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>supp_rec97</t>
+          <t>supp_rec_hi</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -23691,10 +23691,10 @@
         <v>3.779598308668076</v>
       </c>
       <c r="E297" t="n">
-        <v>15.63491357279663</v>
+        <v>15.69920689873691</v>
       </c>
       <c r="F297" t="n">
-        <v>0.3975348405354744</v>
+        <v>0.292113794552554</v>
       </c>
       <c r="G297" t="n">
         <v>450</v>
@@ -23706,7 +23706,7 @@
         <v>30</v>
       </c>
       <c r="J297" t="n">
-        <v>6.639571242589503</v>
+        <v>6.639571242589428</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
@@ -23717,16 +23717,16 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M297" t="n">
-        <v>0.3432088961754882</v>
+        <v>0.4075022221157649</v>
       </c>
       <c r="N297" t="n">
-        <v>1.990553698912876</v>
+        <v>2.257568811347648</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>supp_rec97</t>
+          <t>supp_rec_hi</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -23739,22 +23739,22 @@
         <v>3.316790352504638</v>
       </c>
       <c r="E298" t="n">
-        <v>15.58620003009364</v>
+        <v>15.6540541155105</v>
       </c>
       <c r="F298" t="n">
-        <v>0.3488212978324849</v>
+        <v>0.2469610113261442</v>
       </c>
       <c r="G298" t="n">
         <v>450</v>
       </c>
       <c r="H298" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I298" t="n">
         <v>30</v>
       </c>
       <c r="J298" t="n">
-        <v>6.609105545549926</v>
+        <v>5.82656251900705</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
@@ -23765,16 +23765,16 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M298" t="n">
-        <v>0.2944953534724988</v>
+        <v>0.3623494388893551</v>
       </c>
       <c r="N298" t="n">
-        <v>1.814322884761278</v>
+        <v>2.081818291546431</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>supp_rec97</t>
+          <t>supp_rec_hi</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -23787,22 +23787,22 @@
         <v>2.95495867768595</v>
       </c>
       <c r="E299" t="n">
-        <v>15.54723595089578</v>
+        <v>15.61877249625527</v>
       </c>
       <c r="F299" t="n">
-        <v>0.3098572186346224</v>
+        <v>0.2116793920709181</v>
       </c>
       <c r="G299" t="n">
         <v>450</v>
       </c>
       <c r="H299" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I299" t="n">
         <v>30</v>
       </c>
       <c r="J299" t="n">
-        <v>5.888112213308116</v>
+        <v>5.190937516933554</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
@@ -23813,10 +23813,10 @@
         <v>15.29170467662114</v>
       </c>
       <c r="M299" t="n">
-        <v>0.2555312742746363</v>
+        <v>0.327067819634129</v>
       </c>
       <c r="N299" t="n">
-        <v>1.676646655318585</v>
+        <v>1.944553218920448</v>
       </c>
     </row>
     <row r="300">
@@ -23850,7 +23850,7 @@
         <v>-20</v>
       </c>
       <c r="J300" t="n">
-        <v>13.2159700515131</v>
+        <v>13.21597005151294</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
@@ -23861,10 +23861,10 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M300" t="n">
-        <v>0.1349657630407819</v>
+        <v>0.1349657630407748</v>
       </c>
       <c r="N300" t="n">
-        <v>1.211050516258996</v>
+        <v>1.211050516258978</v>
       </c>
     </row>
     <row r="301">
@@ -23883,10 +23883,10 @@
         <v>6.633580705009276</v>
       </c>
       <c r="E301" t="n">
-        <v>19.16281832625618</v>
+        <v>19.16281832625616</v>
       </c>
       <c r="F301" t="n">
-        <v>0.2524192945236549</v>
+        <v>0.2524192945236514</v>
       </c>
       <c r="G301" t="n">
         <v>425</v>
@@ -23898,7 +23898,7 @@
         <v>-20</v>
       </c>
       <c r="J301" t="n">
-        <v>11.59768800438905</v>
+        <v>11.59768800438891</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
@@ -23909,10 +23909,10 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M301" t="n">
-        <v>0.09412971436285381</v>
+        <v>0.0941297143628432</v>
       </c>
       <c r="N301" t="n">
-        <v>1.1474003127568</v>
+        <v>1.147400312756781</v>
       </c>
     </row>
     <row r="302">
@@ -23931,7 +23931,7 @@
         <v>5.909917355371901</v>
       </c>
       <c r="E302" t="n">
-        <v>19.13101796082532</v>
+        <v>19.13101796082531</v>
       </c>
       <c r="F302" t="n">
         <v>0.2206189290928009</v>
@@ -23946,7 +23946,7 @@
         <v>-20</v>
       </c>
       <c r="J302" t="n">
-        <v>10.33248567663752</v>
+        <v>10.33248567663739</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
@@ -23957,10 +23957,10 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M302" t="n">
-        <v>0.0623293489319998</v>
+        <v>0.0623293489319927</v>
       </c>
       <c r="N302" t="n">
-        <v>1.097673390402009</v>
+        <v>1.097673390401997</v>
       </c>
     </row>
     <row r="303">
@@ -23979,7 +23979,7 @@
         <v>4.724497885835096</v>
       </c>
       <c r="E303" t="n">
-        <v>19.07905355750431</v>
+        <v>19.0790535575043</v>
       </c>
       <c r="F303" t="n">
         <v>0.1686545257717888</v>
@@ -23994,7 +23994,7 @@
         <v>-20</v>
       </c>
       <c r="J303" t="n">
-        <v>8.259981282195689</v>
+        <v>8.259981282195589</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
@@ -24005,10 +24005,10 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M303" t="n">
-        <v>0.0103649456109877</v>
+        <v>0.0103649456109806</v>
       </c>
       <c r="N303" t="n">
-        <v>1.016246047228793</v>
+        <v>1.016246047228783</v>
       </c>
     </row>
     <row r="304">
@@ -24042,7 +24042,7 @@
         <v>-20</v>
       </c>
       <c r="J304" t="n">
-        <v>7.248555002743156</v>
+        <v>7.248555002743068</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
@@ -24053,10 +24053,10 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M304" t="n">
-        <v>-0.015007451885598</v>
+        <v>-0.0150074518856051</v>
       </c>
       <c r="N304" t="n">
-        <v>0.9764879597280476</v>
+        <v>0.9764879597280368</v>
       </c>
     </row>
     <row r="305">
@@ -24090,7 +24090,7 @@
         <v>-20</v>
       </c>
       <c r="J305" t="n">
-        <v>6.457803547898448</v>
+        <v>6.457803547898369</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
@@ -24101,10 +24101,10 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M305" t="n">
-        <v>-0.0348938084026393</v>
+        <v>-0.0348938084026464</v>
       </c>
       <c r="N305" t="n">
-        <v>0.9453698241169411</v>
+        <v>0.9453698241169304</v>
       </c>
     </row>
     <row r="306">
@@ -24123,7 +24123,7 @@
         <v>3.779598308668076</v>
       </c>
       <c r="E306" t="n">
-        <v>19.03757678725126</v>
+        <v>19.03757678725125</v>
       </c>
       <c r="F306" t="n">
         <v>0.127177755518737</v>
@@ -24138,7 +24138,7 @@
         <v>-20</v>
       </c>
       <c r="J306" t="n">
-        <v>6.60798502575655</v>
+        <v>6.60798502575647</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -24149,10 +24149,10 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M306" t="n">
-        <v>-0.031111824642064</v>
+        <v>-0.0311118246420711</v>
       </c>
       <c r="N306" t="n">
-        <v>0.9512833365388436</v>
+        <v>0.951283336538832</v>
       </c>
     </row>
     <row r="307">
@@ -24171,7 +24171,7 @@
         <v>3.316790352504638</v>
       </c>
       <c r="E307" t="n">
-        <v>19.01716102600268</v>
+        <v>19.01716102600267</v>
       </c>
       <c r="F307" t="n">
         <v>0.1067619942701547</v>
@@ -24186,7 +24186,7 @@
         <v>-20</v>
       </c>
       <c r="J307" t="n">
-        <v>5.798844002194524</v>
+        <v>5.798844002194453</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
@@ -24197,10 +24197,10 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M307" t="n">
-        <v>-0.0515275858906463</v>
+        <v>-0.0515275858906534</v>
       </c>
       <c r="N307" t="n">
-        <v>0.9193957377774196</v>
+        <v>0.9193957377774118</v>
       </c>
     </row>
     <row r="308">
@@ -24219,7 +24219,7 @@
         <v>2.95495867768595</v>
       </c>
       <c r="E308" t="n">
-        <v>19.00111109653497</v>
+        <v>19.00111109653496</v>
       </c>
       <c r="F308" t="n">
         <v>0.0907120648024495</v>
@@ -24234,7 +24234,7 @@
         <v>-20</v>
       </c>
       <c r="J308" t="n">
-        <v>5.166242838318758</v>
+        <v>5.166242838318696</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
@@ -24245,16 +24245,16 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M308" t="n">
-        <v>-0.06757751535835151</v>
+        <v>-0.0675775153583586</v>
       </c>
       <c r="N308" t="n">
-        <v>0.8944032116822221</v>
+        <v>0.8944032116822136</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>kaap97</t>
+          <t>kaap_hi</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -24267,10 +24267,10 @@
         <v>7.559196617336151</v>
       </c>
       <c r="E309" t="n">
-        <v>18.89474936961769</v>
+        <v>18.95873683500466</v>
       </c>
       <c r="F309" t="n">
-        <v>0.7377578220652765</v>
+        <v>0.6221431072379389</v>
       </c>
       <c r="G309" t="n">
         <v>425</v>
@@ -24282,7 +24282,7 @@
         <v>-20</v>
       </c>
       <c r="J309" t="n">
-        <v>13.2159700515131</v>
+        <v>13.21597005151294</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
@@ -24293,16 +24293,16 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M309" t="n">
-        <v>-0.1739392422756296</v>
+        <v>-0.1099517768886642</v>
       </c>
       <c r="N309" t="n">
-        <v>0.7298807192144522</v>
+        <v>0.8288483538210301</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>kaap97</t>
+          <t>kaap_hi</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -24315,10 +24315,10 @@
         <v>6.633580705009276</v>
       </c>
       <c r="E310" t="n">
-        <v>18.85391332093976</v>
+        <v>18.91790078632673</v>
       </c>
       <c r="F310" t="n">
-        <v>0.6969217733873485</v>
+        <v>0.5813070585600109</v>
       </c>
       <c r="G310" t="n">
         <v>425</v>
@@ -24330,7 +24330,7 @@
         <v>-20</v>
       </c>
       <c r="J310" t="n">
-        <v>11.59768800438905</v>
+        <v>11.59768800438891</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
@@ -24341,16 +24341,16 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M310" t="n">
-        <v>-0.2147752909535576</v>
+        <v>-0.1507878255665922</v>
       </c>
       <c r="N310" t="n">
-        <v>0.6655218856676183</v>
+        <v>0.7646960538993552</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>kaap97</t>
+          <t>kaap_hi</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -24363,13 +24363,13 @@
         <v>5.909917355371901</v>
       </c>
       <c r="E311" t="n">
-        <v>18.7795133476303</v>
+        <v>18.88610042089588</v>
       </c>
       <c r="F311" t="n">
-        <v>0.6225218000778909</v>
+        <v>0.5495066931291568</v>
       </c>
       <c r="G311" t="n">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="H311" t="n">
         <v>90</v>
@@ -24378,7 +24378,7 @@
         <v>-20</v>
       </c>
       <c r="J311" t="n">
-        <v>29.00156996896854</v>
+        <v>10.33248567663739</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
@@ -24389,16 +24389,16 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M311" t="n">
-        <v>-0.2891752642630152</v>
+        <v>-0.1825881909974462</v>
       </c>
       <c r="N311" t="n">
-        <v>0.6152497793062117</v>
+        <v>0.7146008220433341</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>kaap97</t>
+          <t>kaap_hi</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -24411,10 +24411,10 @@
         <v>4.724497885835096</v>
       </c>
       <c r="E312" t="n">
-        <v>18.6236793131958</v>
+        <v>18.80328149341009</v>
       </c>
       <c r="F312" t="n">
-        <v>0.4666877656433819</v>
+        <v>0.4666877656433748</v>
       </c>
       <c r="G312" t="n">
         <v>400</v>
@@ -24426,7 +24426,7 @@
         <v>-20</v>
       </c>
       <c r="J312" t="n">
-        <v>23.18439459728591</v>
+        <v>23.18439459728572</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
@@ -24437,16 +24437,16 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M312" t="n">
-        <v>-0.4450092986975242</v>
+        <v>-0.2654071184832283</v>
       </c>
       <c r="N312" t="n">
-        <v>0.5330136947337196</v>
+        <v>0.6326816087716471</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>kaap97</t>
+          <t>kaap_hi</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -24459,10 +24459,10 @@
         <v>4.145987940630798</v>
       </c>
       <c r="E313" t="n">
-        <v>18.54915532215126</v>
+        <v>18.72875750236556</v>
       </c>
       <c r="F313" t="n">
-        <v>0.3921637745988455</v>
+        <v>0.3921637745988384</v>
       </c>
       <c r="G313" t="n">
         <v>400</v>
@@ -24474,7 +24474,7 @@
         <v>-20</v>
       </c>
       <c r="J313" t="n">
-        <v>20.34548913639375</v>
+        <v>20.34548913639359</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
@@ -24485,16 +24485,16 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M313" t="n">
-        <v>-0.5195332897420606</v>
+        <v>-0.3399311095277646</v>
       </c>
       <c r="N313" t="n">
-        <v>0.4929477104905125</v>
+        <v>0.5927783972968973</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>kaap97</t>
+          <t>kaap_hi</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -24507,10 +24507,10 @@
         <v>3.693698347107438</v>
       </c>
       <c r="E314" t="n">
-        <v>18.49156970316873</v>
+        <v>18.67117188338303</v>
       </c>
       <c r="F314" t="n">
-        <v>0.3345781556163132</v>
+        <v>0.3345781556163096</v>
       </c>
       <c r="G314" t="n">
         <v>400</v>
@@ -24522,7 +24522,7 @@
         <v>-20</v>
       </c>
       <c r="J314" t="n">
-        <v>18.12598123060534</v>
+        <v>18.12598123060519</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
@@ -24533,16 +24533,16 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M314" t="n">
-        <v>-0.5771189087245929</v>
+        <v>-0.3975167285102934</v>
       </c>
       <c r="N314" t="n">
-        <v>0.4616622970592647</v>
+        <v>0.5616197636447059</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>kaap97</t>
+          <t>kaap_hi</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -24555,10 +24555,10 @@
         <v>3.779598308668076</v>
       </c>
       <c r="E315" t="n">
-        <v>18.50246176367698</v>
+        <v>18.68206394389128</v>
       </c>
       <c r="F315" t="n">
-        <v>0.3454702161245642</v>
+        <v>0.3454702161245606</v>
       </c>
       <c r="G315" t="n">
         <v>400</v>
@@ -24570,7 +24570,7 @@
         <v>-20</v>
       </c>
       <c r="J315" t="n">
-        <v>18.54751567782872</v>
+        <v>18.54751567782857</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
@@ -24581,16 +24581,16 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M315" t="n">
-        <v>-0.5662268482163419</v>
+        <v>-0.3866246680020424</v>
       </c>
       <c r="N315" t="n">
-        <v>0.4676011929907497</v>
+        <v>0.5675348268538175</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>kaap97</t>
+          <t>kaap_hi</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -24603,10 +24603,10 @@
         <v>3.316790352504638</v>
       </c>
       <c r="E316" t="n">
-        <v>18.444018008323</v>
+        <v>18.62362018853729</v>
       </c>
       <c r="F316" t="n">
-        <v>0.2870264607705799</v>
+        <v>0.2870264607705728</v>
       </c>
       <c r="G316" t="n">
         <v>400</v>
@@ -24618,7 +24618,7 @@
         <v>-20</v>
       </c>
       <c r="J316" t="n">
-        <v>16.276391309115</v>
+        <v>16.27639130911486</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
@@ -24629,16 +24629,16 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M316" t="n">
-        <v>-0.6246706035703262</v>
+        <v>-0.4450684233560302</v>
       </c>
       <c r="N316" t="n">
-        <v>0.4356214629163839</v>
+        <v>0.5356805927813395</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>kaap97</t>
+          <t>kaap_hi</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -24651,10 +24651,10 @@
         <v>2.95495867768595</v>
       </c>
       <c r="E317" t="n">
-        <v>18.39871863363259</v>
+        <v>18.57832081384689</v>
       </c>
       <c r="F317" t="n">
-        <v>0.241727086080175</v>
+        <v>0.2417270860801714</v>
       </c>
       <c r="G317" t="n">
         <v>400</v>
@@ -24666,7 +24666,7 @@
         <v>-20</v>
       </c>
       <c r="J317" t="n">
-        <v>14.50078498448427</v>
+        <v>14.50078498448415</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
@@ -24677,10 +24677,10 @@
         <v>19.06868861189332</v>
       </c>
       <c r="M317" t="n">
-        <v>-0.6699699782607311</v>
+        <v>-0.4903677980464316</v>
       </c>
       <c r="N317" t="n">
-        <v>0.4106514740290691</v>
+        <v>0.5108003938487056</v>
       </c>
     </row>
     <row r="320">
